--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -608,8 +608,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>1.35</v>
+      <c r="J3" s="3" t="n">
+        <v>1.54</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,43 +805,43 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -853,8 +853,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n">
-        <v>1.54</v>
+      <c r="J8" s="4" t="n">
+        <v>1.37</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -951,8 +951,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n">
-        <v>1.47</v>
+      <c r="J10" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,43 +1050,43 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1294,8 +1294,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="3" t="n">
-        <v>1.5</v>
+      <c r="J17" s="4" t="n">
+        <v>1.38</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1343,8 +1343,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n">
-        <v>1.45</v>
+      <c r="J18" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1392,8 +1392,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="3" t="n">
-        <v>1.52</v>
+      <c r="J19" s="4" t="n">
+        <v>1.45</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1588,8 +1588,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="3" t="n">
-        <v>1.53</v>
+      <c r="J23" s="4" t="n">
+        <v>1.25</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1931,7 +1931,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="J30" s="3" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -1941,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1988,32 +1990,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2035,32 +2037,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2082,32 +2084,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2129,32 +2131,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2176,32 +2178,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2223,32 +2225,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2270,32 +2272,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2317,32 +2319,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2364,32 +2366,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2411,32 +2413,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2458,32 +2460,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2505,32 +2507,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2544,6 +2546,53 @@
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -657,8 +657,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>1.35</v>
+      <c r="J4" s="3" t="n">
+        <v>1.54</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,43 +854,43 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -902,8 +902,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="3" t="n">
-        <v>1.54</v>
+      <c r="J9" s="4" t="n">
+        <v>1.37</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1000,8 +1000,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n">
-        <v>1.47</v>
+      <c r="J11" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,43 +1099,43 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1343,8 +1343,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J18" s="3" t="n">
-        <v>1.5</v>
+      <c r="J18" s="4" t="n">
+        <v>1.38</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1392,8 +1392,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n">
-        <v>1.45</v>
+      <c r="J19" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1441,8 +1441,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="3" t="n">
-        <v>1.52</v>
+      <c r="J20" s="4" t="n">
+        <v>1.45</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1539,8 +1539,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="4" t="n">
-        <v>1.49</v>
+      <c r="J22" s="3" t="n">
+        <v>1.52</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1637,8 +1637,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="3" t="n">
-        <v>1.53</v>
+      <c r="J24" s="4" t="n">
+        <v>1.25</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1980,7 +1980,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr"/>
+      <c r="J31" s="3" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -1990,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2037,32 +2039,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2084,32 +2086,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2131,32 +2133,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2178,32 +2180,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2225,32 +2227,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2272,32 +2274,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2319,32 +2321,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2366,32 +2368,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2413,32 +2415,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2460,32 +2462,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2507,32 +2509,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2554,32 +2556,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2593,6 +2595,53 @@
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,28 +522,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -706,8 +706,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>1.35</v>
+      <c r="J5" s="3" t="n">
+        <v>1.54</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,43 +903,43 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -951,8 +951,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="3" t="n">
-        <v>1.54</v>
+      <c r="J10" s="4" t="n">
+        <v>1.37</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1049,8 +1049,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="4" t="n">
-        <v>1.47</v>
+      <c r="J12" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,43 +1148,43 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1392,8 +1392,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="3" t="n">
-        <v>1.5</v>
+      <c r="J19" s="4" t="n">
+        <v>1.38</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1441,8 +1441,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n">
-        <v>1.45</v>
+      <c r="J20" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1490,8 +1490,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J21" s="3" t="n">
-        <v>1.52</v>
+      <c r="J21" s="4" t="n">
+        <v>1.45</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1588,8 +1588,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n">
-        <v>1.49</v>
+      <c r="J23" s="3" t="n">
+        <v>1.52</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1686,8 +1686,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="3" t="n">
-        <v>1.53</v>
+      <c r="J25" s="4" t="n">
+        <v>1.25</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2029,7 +2029,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="J32" s="3" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2039,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2086,32 +2088,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2133,32 +2135,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2180,32 +2182,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2227,32 +2229,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2274,32 +2276,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2321,32 +2323,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2368,32 +2370,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2415,32 +2417,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2462,32 +2464,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2509,32 +2511,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2556,32 +2558,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2603,32 +2605,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2642,6 +2644,53 @@
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -38,14 +38,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,28 +571,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -608,8 +608,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>1.6</v>
+      <c r="J3" s="4" t="n">
+        <v>1.56</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -657,8 +657,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>1.53</v>
+      <c r="J4" s="4" t="n">
+        <v>1.6</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -706,8 +706,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>1.54</v>
+      <c r="J5" s="4" t="n">
+        <v>1.53</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -804,8 +804,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
-        <v>1.42</v>
+      <c r="J7" s="3" t="n">
+        <v>1.35</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -853,8 +853,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n">
-        <v>1.32</v>
+      <c r="J8" s="3" t="n">
+        <v>1.42</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -902,8 +902,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>1.34</v>
+      <c r="J9" s="3" t="n">
+        <v>1.32</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -951,44 +951,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n">
-        <v>1.37</v>
+      <c r="J10" s="3" t="n">
+        <v>1.34</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1049,8 +1049,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="3" t="n">
-        <v>1.5</v>
+      <c r="J12" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1147,8 +1147,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J14" s="4" t="n">
-        <v>1.26</v>
+      <c r="J14" s="3" t="n">
+        <v>1.47</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1196,44 +1196,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n">
-        <v>1.22</v>
+      <c r="J15" s="3" t="n">
+        <v>1.26</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1245,8 +1245,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="4" t="n">
-        <v>1.19</v>
+      <c r="J16" s="3" t="n">
+        <v>1.22</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1294,8 +1294,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n">
-        <v>1.37</v>
+      <c r="J17" s="3" t="n">
+        <v>1.19</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1343,8 +1343,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n">
-        <v>1.41</v>
+      <c r="J18" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1392,8 +1392,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n">
-        <v>1.38</v>
+      <c r="J19" s="3" t="n">
+        <v>1.41</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="3" t="n">
+      <c r="J23" s="4" t="n">
         <v>1.52</v>
       </c>
       <c r="K23" t="inlineStr">
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1686,8 +1686,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
-        <v>1.25</v>
+      <c r="J25" s="3" t="n">
+        <v>1.49</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1784,8 +1784,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="3" t="n">
-        <v>1.84</v>
+      <c r="J27" s="4" t="n">
+        <v>1.53</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1833,8 +1833,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="3" t="n">
-        <v>1.83</v>
+      <c r="J28" s="4" t="n">
+        <v>1.84</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1882,8 +1882,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="3" t="n">
-        <v>1.77</v>
+      <c r="J29" s="4" t="n">
+        <v>1.83</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1931,8 +1931,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="3" t="n">
-        <v>1.64</v>
+      <c r="J30" s="4" t="n">
+        <v>1.77</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1980,8 +1980,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="3" t="n">
-        <v>1.71</v>
+      <c r="J31" s="4" t="n">
+        <v>1.64</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2029,8 +2029,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J32" s="3" t="n">
-        <v>1.63</v>
+      <c r="J32" s="4" t="n">
+        <v>1.71</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2078,7 +2078,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="J33" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2088,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2135,32 +2137,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2182,32 +2184,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2229,32 +2231,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2276,32 +2278,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2323,32 +2325,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2370,32 +2372,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2417,32 +2419,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2464,32 +2466,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2511,32 +2513,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2558,32 +2560,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2605,32 +2607,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2652,32 +2654,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2691,6 +2693,53 @@
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -38,14 +38,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,28 +620,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -657,8 +657,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>1.6</v>
+      <c r="J4" s="3" t="n">
+        <v>1.56</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -706,8 +706,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>1.53</v>
+      <c r="J5" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -755,8 +755,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>1.54</v>
+      <c r="J6" s="3" t="n">
+        <v>1.53</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -853,8 +853,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n">
-        <v>1.42</v>
+      <c r="J8" s="4" t="n">
+        <v>1.35</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -902,8 +902,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="3" t="n">
-        <v>1.32</v>
+      <c r="J9" s="4" t="n">
+        <v>1.42</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -951,8 +951,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="3" t="n">
-        <v>1.34</v>
+      <c r="J10" s="4" t="n">
+        <v>1.32</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1000,44 +1000,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="3" t="n">
-        <v>1.37</v>
+      <c r="J11" s="4" t="n">
+        <v>1.34</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1098,8 +1098,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n">
-        <v>1.5</v>
+      <c r="J13" s="3" t="n">
+        <v>1.54</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1196,8 +1196,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="3" t="n">
-        <v>1.26</v>
+      <c r="J15" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1245,44 +1245,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="3" t="n">
-        <v>1.22</v>
+      <c r="J16" s="4" t="n">
+        <v>1.26</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1294,8 +1294,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="3" t="n">
-        <v>1.19</v>
+      <c r="J17" s="4" t="n">
+        <v>1.22</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1343,8 +1343,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J18" s="3" t="n">
-        <v>1.37</v>
+      <c r="J18" s="4" t="n">
+        <v>1.19</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1392,8 +1392,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="3" t="n">
-        <v>1.41</v>
+      <c r="J19" s="4" t="n">
+        <v>1.37</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1441,8 +1441,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="3" t="n">
-        <v>1.38</v>
+      <c r="J20" s="4" t="n">
+        <v>1.41</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n">
+      <c r="J24" s="3" t="n">
         <v>1.52</v>
       </c>
       <c r="K24" t="inlineStr">
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1735,8 +1735,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="3" t="n">
-        <v>1.25</v>
+      <c r="J26" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1833,8 +1833,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n">
-        <v>1.84</v>
+      <c r="J28" s="3" t="n">
+        <v>1.53</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1882,8 +1882,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n">
-        <v>1.83</v>
+      <c r="J29" s="3" t="n">
+        <v>1.84</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1931,8 +1931,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n">
-        <v>1.77</v>
+      <c r="J30" s="3" t="n">
+        <v>1.83</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1980,8 +1980,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
-        <v>1.64</v>
+      <c r="J31" s="3" t="n">
+        <v>1.77</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2029,8 +2029,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J32" s="4" t="n">
-        <v>1.71</v>
+      <c r="J32" s="3" t="n">
+        <v>1.64</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2078,8 +2078,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n">
-        <v>1.63</v>
+      <c r="J33" s="3" t="n">
+        <v>1.71</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2127,7 +2127,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
+      <c r="J34" s="3" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2137,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2184,32 +2186,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2231,32 +2233,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2278,32 +2280,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2325,32 +2327,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2372,32 +2374,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2419,32 +2421,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2466,32 +2468,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2513,32 +2515,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2560,32 +2562,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2607,32 +2609,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2654,32 +2656,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2701,32 +2703,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2740,6 +2742,53 @@
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -38,14 +38,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,28 +669,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -706,8 +706,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>1.6</v>
+      <c r="J5" s="4" t="n">
+        <v>1.56</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -755,8 +755,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>1.53</v>
+      <c r="J6" s="4" t="n">
+        <v>1.6</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -804,8 +804,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n">
-        <v>1.54</v>
+      <c r="J7" s="4" t="n">
+        <v>1.53</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -902,8 +902,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>1.42</v>
+      <c r="J9" s="3" t="n">
+        <v>1.35</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -951,8 +951,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n">
-        <v>1.32</v>
+      <c r="J10" s="3" t="n">
+        <v>1.42</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1000,8 +1000,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n">
-        <v>1.34</v>
+      <c r="J11" s="3" t="n">
+        <v>1.32</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1049,44 +1049,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="4" t="n">
-        <v>1.37</v>
+      <c r="J12" s="3" t="n">
+        <v>1.34</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1147,8 +1147,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>1.5</v>
+      <c r="J14" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1245,8 +1245,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="4" t="n">
-        <v>1.26</v>
+      <c r="J16" s="3" t="n">
+        <v>1.47</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1294,44 +1294,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n">
-        <v>1.22</v>
+      <c r="J17" s="3" t="n">
+        <v>1.26</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1343,8 +1343,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n">
-        <v>1.19</v>
+      <c r="J18" s="3" t="n">
+        <v>1.22</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1392,8 +1392,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n">
-        <v>1.37</v>
+      <c r="J19" s="3" t="n">
+        <v>1.19</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1441,8 +1441,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n">
-        <v>1.41</v>
+      <c r="J20" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1490,8 +1490,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n">
-        <v>1.38</v>
+      <c r="J21" s="3" t="n">
+        <v>1.41</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="3" t="n">
+      <c r="J25" s="4" t="n">
         <v>1.52</v>
       </c>
       <c r="K25" t="inlineStr">
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1784,8 +1784,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n">
-        <v>1.25</v>
+      <c r="J27" s="3" t="n">
+        <v>1.49</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1882,8 +1882,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="3" t="n">
-        <v>1.84</v>
+      <c r="J29" s="4" t="n">
+        <v>1.53</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1931,8 +1931,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="3" t="n">
-        <v>1.83</v>
+      <c r="J30" s="4" t="n">
+        <v>1.84</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1980,8 +1980,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="3" t="n">
-        <v>1.77</v>
+      <c r="J31" s="4" t="n">
+        <v>1.83</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2029,8 +2029,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J32" s="3" t="n">
-        <v>1.64</v>
+      <c r="J32" s="4" t="n">
+        <v>1.77</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2078,8 +2078,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J33" s="3" t="n">
-        <v>1.71</v>
+      <c r="J33" s="4" t="n">
+        <v>1.64</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2127,8 +2127,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J34" s="3" t="n">
-        <v>1.63</v>
+      <c r="J34" s="4" t="n">
+        <v>1.71</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2176,7 +2176,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
+      <c r="J35" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2186,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2233,32 +2235,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2280,32 +2282,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2327,32 +2329,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2374,32 +2376,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2421,32 +2423,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2468,32 +2470,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2515,32 +2517,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2562,32 +2564,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2609,32 +2611,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2656,32 +2658,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2703,32 +2705,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2750,32 +2752,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2789,6 +2791,53 @@
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4392.71</v>
+        <v>4336.36</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4431.4</v>
+        <v>4374.3</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>38.69</v>
+        <v>37.94</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4362.36</v>
+        <v>4338.92</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4402</v>
+        <v>4376.9</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>39.64</v>
+        <v>37.98</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -608,8 +608,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>1.55</v>
+      <c r="J3" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4348.5</v>
+        <v>4392.71</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4390.5</v>
+        <v>4431.4</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>42</v>
+        <v>38.69</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4297.04</v>
+        <v>4362.36</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4337.8</v>
+        <v>4402</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>40.76</v>
+        <v>39.64</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4308.94</v>
+        <v>4348.5</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4349.7</v>
+        <v>4390.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -755,8 +755,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>1.6</v>
+      <c r="J6" s="3" t="n">
+        <v>1.49</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4368.9</v>
+        <v>4297.04</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4411.5</v>
+        <v>4337.8</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4362.82</v>
+        <v>4308.94</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4404.4</v>
+        <v>4349.7</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>41.58</v>
+        <v>40.76</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4412.58</v>
+        <v>4368.9</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4457.7</v>
+        <v>4411.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>45.12</v>
+        <v>42.6</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -902,8 +902,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="3" t="n">
-        <v>1.35</v>
+      <c r="J9" s="4" t="n">
+        <v>1.53</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4391.69</v>
+        <v>4362.82</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4436.1</v>
+        <v>4404.4</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>44.41</v>
+        <v>41.58</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -951,8 +951,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="3" t="n">
-        <v>1.42</v>
+      <c r="J10" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4424</v>
+        <v>4412.58</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4471.5</v>
+        <v>4457.7</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>47.5</v>
+        <v>45.12</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4491.75</v>
+        <v>4391.69</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4539.2</v>
+        <v>4436.1</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>47.45</v>
+        <v>44.41</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4368.02</v>
+        <v>4424</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4414.7</v>
+        <v>4471.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>46.68</v>
+        <v>47.5</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,43 +1099,43 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4347.7</v>
+        <v>4491.75</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4395.8</v>
+        <v>4539.2</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>48.1</v>
+        <v>47.45</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1147,44 +1147,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J14" s="4" t="n">
-        <v>1.54</v>
+      <c r="J14" s="3" t="n">
+        <v>1.34</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4432.42</v>
+        <v>4368.02</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4482.1</v>
+        <v>4414.7</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>49.68</v>
+        <v>46.68</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1196,8 +1196,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n">
-        <v>1.5</v>
+      <c r="J15" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4478.51</v>
+        <v>4347.7</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4528.9</v>
+        <v>4395.8</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>50.39</v>
+        <v>48.1</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1245,8 +1245,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="3" t="n">
-        <v>1.47</v>
+      <c r="J16" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4610.08</v>
+        <v>4432.42</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4663.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>53.82</v>
+        <v>49.68</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1294,8 +1294,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="3" t="n">
-        <v>1.26</v>
+      <c r="J17" s="4" t="n">
+        <v>1.5</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4600.96</v>
+        <v>4478.51</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4656.3</v>
+        <v>4528.9</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>55.34</v>
+        <v>50.39</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,43 +1344,43 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4638.15</v>
+        <v>4610.08</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4695.7</v>
+        <v>4663.9</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>57.55</v>
+        <v>53.82</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1393,43 +1393,43 @@
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4637.46</v>
+        <v>4600.96</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4694.5</v>
+        <v>4656.3</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>57.04</v>
+        <v>55.34</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4620.76</v>
+        <v>4638.15</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4678.6</v>
+        <v>4695.7</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>57.84</v>
+        <v>57.55</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4518.38</v>
+        <v>4637.46</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4575</v>
+        <v>4694.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>56.62</v>
+        <v>57.04</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4488.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4545.9</v>
+        <v>4678.6</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>57.52</v>
+        <v>57.84</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1588,8 +1588,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n">
-        <v>1.5</v>
+      <c r="J23" s="3" t="n">
+        <v>1.41</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4364.25</v>
+        <v>4518.38</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4420.1</v>
+        <v>4575</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>55.85</v>
+        <v>56.62</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4417.13</v>
+        <v>4488.38</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4474.7</v>
+        <v>4545.9</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>57.57</v>
+        <v>57.52</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4382.43</v>
+        <v>4364.25</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4440.3</v>
+        <v>4420.1</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>57.87</v>
+        <v>55.85</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1735,8 +1735,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>1.52</v>
+      <c r="J26" s="3" t="n">
+        <v>1.45</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4360.96</v>
+        <v>4417.13</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4417.6</v>
+        <v>4474.7</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>56.64</v>
+        <v>57.57</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1784,8 +1784,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="3" t="n">
-        <v>1.49</v>
+      <c r="J27" s="4" t="n">
+        <v>1.52</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4410.25</v>
+        <v>4382.43</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4470.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>60.35</v>
+        <v>57.87</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1833,8 +1833,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="3" t="n">
-        <v>1.25</v>
+      <c r="J28" s="4" t="n">
+        <v>1.52</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4376.76</v>
+        <v>4360.96</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4436.1</v>
+        <v>4417.6</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>59.34</v>
+        <v>56.64</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1882,8 +1882,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n">
-        <v>1.53</v>
+      <c r="J29" s="3" t="n">
+        <v>1.49</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4362.03</v>
+        <v>4410.25</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4421.7</v>
+        <v>4470.6</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>59.67</v>
+        <v>60.35</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1931,8 +1931,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n">
-        <v>1.84</v>
+      <c r="J30" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4336.77</v>
+        <v>4376.76</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4396</v>
+        <v>4436.1</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>59.23</v>
+        <v>59.34</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4240.53</v>
+        <v>4362.03</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4298.8</v>
+        <v>4421.7</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>58.27</v>
+        <v>59.67</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4248.17</v>
+        <v>4336.77</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4308.3</v>
+        <v>4396</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>60.13</v>
+        <v>59.23</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4093.57</v>
+        <v>4240.53</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4150.6</v>
+        <v>4298.8</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>57.03</v>
+        <v>58.27</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4034.98</v>
+        <v>4248.17</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4090.7</v>
+        <v>4308.3</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>55.72</v>
+        <v>60.13</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4047.78</v>
+        <v>4093.57</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4104.3</v>
+        <v>4150.6</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>56.52</v>
+        <v>57.03</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2225,7 +2225,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="J36" s="4" t="n">
+        <v>1.71</v>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2235,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4100.74</v>
+        <v>4034.98</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4159.8</v>
+        <v>4090.7</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>59.06</v>
+        <v>55.72</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2272,7 +2274,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr"/>
+      <c r="J37" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2282,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4038.59</v>
+        <v>4047.78</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4096.6</v>
+        <v>4104.3</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>58.01</v>
+        <v>56.52</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2329,32 +2333,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4035.01</v>
+        <v>4100.74</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4095.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>60.59</v>
+        <v>59.06</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2376,32 +2380,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4073.78</v>
+        <v>4038.59</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4134.8</v>
+        <v>4096.6</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>61.02</v>
+        <v>58.01</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2423,32 +2427,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4068.52</v>
+        <v>4035.01</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4130.3</v>
+        <v>4095.6</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>61.78</v>
+        <v>60.59</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2470,32 +2474,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4047.38</v>
+        <v>4073.78</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4108.8</v>
+        <v>4134.8</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>61.42</v>
+        <v>61.02</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2517,32 +2521,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4144.43</v>
+        <v>4068.52</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4210.7</v>
+        <v>4130.3</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>66.27</v>
+        <v>61.78</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2564,32 +2568,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4070.53</v>
+        <v>4047.38</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4132.1</v>
+        <v>4108.8</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>61.57</v>
+        <v>61.42</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2611,32 +2615,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4012.2</v>
+        <v>4144.43</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4073.4</v>
+        <v>4210.7</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>61.2</v>
+        <v>66.27</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2658,32 +2662,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4012.43</v>
+        <v>4070.53</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4073.6</v>
+        <v>4132.1</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>61.17</v>
+        <v>61.57</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2705,32 +2709,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3984.41</v>
+        <v>4012.2</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4045.5</v>
+        <v>4073.4</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>61.09</v>
+        <v>61.2</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2752,32 +2756,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4054.39</v>
+        <v>4012.43</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4119.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>65.11</v>
+        <v>61.17</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2799,32 +2803,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4062.2</v>
+        <v>3984.41</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4127.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>65.3</v>
+        <v>61.09</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2838,6 +2842,100 @@
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>4054.39</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>-0.19%</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>$-8.81</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>4119.5</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>-0.19%</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>65.11</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -706,8 +706,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>1.55</v>
+      <c r="J5" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -755,8 +755,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>1.49</v>
+      <c r="J6" s="4" t="n">
+        <v>1.55</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -804,8 +804,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
-        <v>1.56</v>
+      <c r="J7" s="3" t="n">
+        <v>1.49</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,28 +816,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1000,8 +1000,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="3" t="n">
-        <v>1.35</v>
+      <c r="J11" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,43 +1197,43 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1245,8 +1245,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="4" t="n">
-        <v>1.54</v>
+      <c r="J16" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1343,8 +1343,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J18" s="3" t="n">
-        <v>1.47</v>
+      <c r="J18" s="4" t="n">
+        <v>1.5</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,43 +1442,43 @@
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1686,8 +1686,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
-        <v>1.5</v>
+      <c r="J25" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1735,8 +1735,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="3" t="n">
-        <v>1.45</v>
+      <c r="J26" s="4" t="n">
+        <v>1.5</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1784,8 +1784,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n">
-        <v>1.52</v>
+      <c r="J27" s="3" t="n">
+        <v>1.45</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1882,8 +1882,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="3" t="n">
-        <v>1.49</v>
+      <c r="J29" s="4" t="n">
+        <v>1.52</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1980,8 +1980,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
-        <v>1.53</v>
+      <c r="J31" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2323,7 +2323,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
+      <c r="J38" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2333,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2380,32 +2382,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2427,32 +2429,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2474,32 +2476,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2521,32 +2523,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2568,32 +2570,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2615,32 +2617,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2662,32 +2664,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2709,32 +2711,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2756,32 +2758,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2803,32 +2805,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2850,32 +2852,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2897,32 +2899,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2936,6 +2938,53 @@
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -755,8 +755,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>1.55</v>
+      <c r="J6" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -804,8 +804,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n">
-        <v>1.49</v>
+      <c r="J7" s="4" t="n">
+        <v>1.55</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,28 +865,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1049,8 +1049,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="3" t="n">
-        <v>1.35</v>
+      <c r="J12" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,43 +1246,43 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1294,8 +1294,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n">
-        <v>1.54</v>
+      <c r="J17" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1392,8 +1392,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="3" t="n">
-        <v>1.47</v>
+      <c r="J19" s="4" t="n">
+        <v>1.5</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,43 +1491,43 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1735,8 +1735,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>1.5</v>
+      <c r="J26" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1784,8 +1784,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="3" t="n">
-        <v>1.45</v>
+      <c r="J27" s="4" t="n">
+        <v>1.5</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1833,8 +1833,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n">
-        <v>1.52</v>
+      <c r="J28" s="3" t="n">
+        <v>1.45</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1931,8 +1931,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="3" t="n">
-        <v>1.49</v>
+      <c r="J30" s="4" t="n">
+        <v>1.52</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1980,8 +1980,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="3" t="n">
-        <v>1.25</v>
+      <c r="J31" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2029,8 +2029,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J32" s="4" t="n">
-        <v>1.53</v>
+      <c r="J32" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2372,7 +2372,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr"/>
+      <c r="J39" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2382,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2429,32 +2431,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2476,32 +2478,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2523,32 +2525,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2570,32 +2572,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2617,32 +2619,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2664,32 +2666,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2711,32 +2713,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2758,32 +2760,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2805,32 +2807,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2852,32 +2854,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2899,32 +2901,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2946,32 +2948,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2985,6 +2987,53 @@
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -804,8 +804,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
-        <v>1.55</v>
+      <c r="J7" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,28 +914,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1098,8 +1098,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J13" s="3" t="n">
-        <v>1.35</v>
+      <c r="J13" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,43 +1295,43 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1343,8 +1343,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n">
-        <v>1.54</v>
+      <c r="J18" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1441,8 +1441,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="3" t="n">
-        <v>1.47</v>
+      <c r="J20" s="4" t="n">
+        <v>1.5</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1490,8 +1490,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J21" s="3" t="n">
-        <v>1.26</v>
+      <c r="J21" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,43 +1540,43 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1784,8 +1784,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n">
-        <v>1.5</v>
+      <c r="J27" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1833,8 +1833,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="3" t="n">
-        <v>1.45</v>
+      <c r="J28" s="4" t="n">
+        <v>1.5</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1882,8 +1882,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n">
-        <v>1.52</v>
+      <c r="J29" s="3" t="n">
+        <v>1.45</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2029,8 +2029,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J32" s="3" t="n">
-        <v>1.25</v>
+      <c r="J32" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2078,8 +2078,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n">
-        <v>1.53</v>
+      <c r="J33" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2421,7 +2421,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr"/>
+      <c r="J40" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2431,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2478,32 +2480,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2525,32 +2527,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2572,32 +2574,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2619,32 +2621,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2666,32 +2668,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2713,32 +2715,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2760,32 +2762,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2807,32 +2809,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2854,32 +2856,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2901,32 +2903,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2948,32 +2950,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2995,32 +2997,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3034,6 +3036,53 @@
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -853,8 +853,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n">
-        <v>1.55</v>
+      <c r="J8" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,28 +963,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1147,8 +1147,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>1.35</v>
+      <c r="J14" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,43 +1344,43 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1392,8 +1392,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n">
-        <v>1.54</v>
+      <c r="J19" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1539,8 +1539,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="3" t="n">
-        <v>1.26</v>
+      <c r="J22" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,43 +1589,43 @@
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1833,8 +1833,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n">
-        <v>1.5</v>
+      <c r="J28" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1882,8 +1882,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="3" t="n">
-        <v>1.45</v>
+      <c r="J29" s="4" t="n">
+        <v>1.5</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1931,8 +1931,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n">
-        <v>1.52</v>
+      <c r="J30" s="3" t="n">
+        <v>1.45</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2078,8 +2078,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J33" s="3" t="n">
-        <v>1.25</v>
+      <c r="J33" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2127,8 +2127,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J34" s="4" t="n">
-        <v>1.53</v>
+      <c r="J34" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J40" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2470,7 +2470,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr"/>
+      <c r="J41" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2480,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2527,32 +2529,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2574,32 +2576,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2621,32 +2623,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2668,32 +2670,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2715,32 +2717,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2762,32 +2764,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2809,32 +2811,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2856,32 +2858,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2903,32 +2905,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2950,32 +2952,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2997,32 +2999,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3044,32 +3046,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3083,6 +3085,53 @@
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -902,8 +902,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>1.55</v>
+      <c r="J9" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,28 +1012,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1196,8 +1196,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="3" t="n">
-        <v>1.35</v>
+      <c r="J15" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1393,43 +1393,43 @@
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1441,8 +1441,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n">
-        <v>1.54</v>
+      <c r="J20" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1588,8 +1588,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="3" t="n">
-        <v>1.26</v>
+      <c r="J23" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,43 +1638,43 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1882,8 +1882,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n">
-        <v>1.5</v>
+      <c r="J29" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1931,8 +1931,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="3" t="n">
-        <v>1.45</v>
+      <c r="J30" s="4" t="n">
+        <v>1.5</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1980,8 +1980,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
-        <v>1.52</v>
+      <c r="J31" s="3" t="n">
+        <v>1.45</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2127,8 +2127,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J34" s="3" t="n">
-        <v>1.25</v>
+      <c r="J34" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2176,8 +2176,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n">
-        <v>1.53</v>
+      <c r="J35" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J40" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2519,7 +2519,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr"/>
+      <c r="J42" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2529,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2576,32 +2578,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2623,32 +2625,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2670,32 +2672,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2717,32 +2719,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2764,32 +2766,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2811,32 +2813,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2858,32 +2860,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2905,32 +2907,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2952,32 +2954,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2999,32 +3001,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3046,32 +3048,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3093,32 +3095,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3132,6 +3134,53 @@
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -951,8 +951,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n">
-        <v>1.55</v>
+      <c r="J10" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,28 +1061,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1245,8 +1245,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="3" t="n">
-        <v>1.35</v>
+      <c r="J16" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,43 +1442,43 @@
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1490,8 +1490,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n">
-        <v>1.54</v>
+      <c r="J21" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1637,8 +1637,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="3" t="n">
-        <v>1.26</v>
+      <c r="J24" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,43 +1687,43 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1931,8 +1931,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n">
-        <v>1.5</v>
+      <c r="J30" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1980,8 +1980,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="3" t="n">
-        <v>1.45</v>
+      <c r="J31" s="4" t="n">
+        <v>1.5</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2176,8 +2176,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J35" s="3" t="n">
-        <v>1.25</v>
+      <c r="J35" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2225,8 +2225,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J36" s="4" t="n">
-        <v>1.53</v>
+      <c r="J36" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J40" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2568,7 +2568,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr"/>
+      <c r="J43" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2578,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2625,32 +2627,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2672,32 +2674,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2719,32 +2721,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2766,32 +2768,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2813,32 +2815,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2860,32 +2862,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2907,32 +2909,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2954,32 +2956,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3001,32 +3003,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3048,32 +3050,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3095,32 +3097,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3142,32 +3144,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3181,6 +3183,53 @@
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1000,8 +1000,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n">
-        <v>1.55</v>
+      <c r="J11" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,28 +1110,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1294,8 +1294,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="3" t="n">
-        <v>1.35</v>
+      <c r="J17" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1392,8 +1392,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="3" t="n">
-        <v>1.32</v>
+      <c r="J19" s="4" t="n">
+        <v>1.42</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,43 +1491,43 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1539,8 +1539,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="4" t="n">
-        <v>1.54</v>
+      <c r="J22" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1686,8 +1686,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="3" t="n">
-        <v>1.26</v>
+      <c r="J25" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,43 +1736,43 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1980,8 +1980,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
-        <v>1.5</v>
+      <c r="J31" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2225,8 +2225,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J36" s="3" t="n">
-        <v>1.25</v>
+      <c r="J36" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2274,8 +2274,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J37" s="4" t="n">
-        <v>1.53</v>
+      <c r="J37" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J40" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2617,7 +2617,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr"/>
+      <c r="J44" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2627,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2674,32 +2676,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2721,32 +2723,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2768,32 +2770,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2815,32 +2817,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2862,32 +2864,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2909,32 +2911,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2956,32 +2958,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3003,32 +3005,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3050,32 +3052,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3097,32 +3099,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3144,32 +3146,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3191,32 +3193,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3230,6 +3232,53 @@
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1049,8 +1049,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="4" t="n">
-        <v>1.55</v>
+      <c r="J12" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,28 +1159,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1343,8 +1343,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J18" s="3" t="n">
-        <v>1.35</v>
+      <c r="J18" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1392,8 +1392,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n">
-        <v>1.42</v>
+      <c r="J19" s="3" t="n">
+        <v>1.35</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1441,8 +1441,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="3" t="n">
-        <v>1.32</v>
+      <c r="J20" s="4" t="n">
+        <v>1.42</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,43 +1540,43 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1588,8 +1588,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n">
-        <v>1.54</v>
+      <c r="J23" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1735,8 +1735,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="3" t="n">
-        <v>1.26</v>
+      <c r="J26" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,43 +1785,43 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2029,8 +2029,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J32" s="4" t="n">
-        <v>1.5</v>
+      <c r="J32" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2274,8 +2274,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J37" s="3" t="n">
-        <v>1.25</v>
+      <c r="J37" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2323,8 +2323,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J38" s="4" t="n">
-        <v>1.53</v>
+      <c r="J38" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J40" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2666,7 +2666,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr"/>
+      <c r="J45" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2676,32 +2678,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2723,32 +2725,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2770,32 +2772,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2817,32 +2819,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2864,32 +2866,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2911,32 +2913,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2958,32 +2960,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3005,32 +3007,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3052,32 +3054,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3099,32 +3101,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3146,32 +3148,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3193,32 +3195,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3240,32 +3242,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3279,6 +3281,53 @@
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4139.21</v>
+        <v>4129.15</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>+$1.31</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4167.9</v>
+        <v>4156.7</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>28.69</v>
+        <v>27.55</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1098,8 +1098,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n">
-        <v>1.55</v>
+      <c r="J13" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,28 +1208,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1392,8 +1392,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="3" t="n">
-        <v>1.35</v>
+      <c r="J19" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1441,8 +1441,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n">
-        <v>1.42</v>
+      <c r="J20" s="3" t="n">
+        <v>1.35</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1490,8 +1490,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J21" s="3" t="n">
-        <v>1.32</v>
+      <c r="J21" s="4" t="n">
+        <v>1.42</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,43 +1589,43 @@
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1637,8 +1637,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n">
-        <v>1.54</v>
+      <c r="J24" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1784,8 +1784,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="3" t="n">
-        <v>1.26</v>
+      <c r="J27" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1834,43 +1834,43 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2078,8 +2078,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n">
-        <v>1.5</v>
+      <c r="J33" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2323,8 +2323,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J38" s="3" t="n">
-        <v>1.25</v>
+      <c r="J38" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2372,8 +2372,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J39" s="4" t="n">
-        <v>1.53</v>
+      <c r="J39" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J40" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2678,32 +2678,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2715,7 +2715,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr"/>
+      <c r="J46" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2725,32 +2727,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2772,32 +2774,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2819,32 +2821,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2866,32 +2868,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2913,32 +2915,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2960,32 +2962,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3007,32 +3009,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3054,32 +3056,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3101,32 +3103,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3148,32 +3150,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3195,32 +3197,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3242,32 +3244,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3289,32 +3291,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3328,6 +3330,53 @@
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4129.15</v>
+        <v>4162.96</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$1.31</t>
+          <t>+$13.14</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4156.7</v>
+        <v>4190.3</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>27.55</v>
+        <v>27.34</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4139.21</v>
+        <v>4129.15</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>+$1.31</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4167.9</v>
+        <v>4156.7</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>28.69</v>
+        <v>27.55</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1147,8 +1147,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J14" s="4" t="n">
-        <v>1.55</v>
+      <c r="J14" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,28 +1257,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1441,8 +1441,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="3" t="n">
-        <v>1.35</v>
+      <c r="J20" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1490,8 +1490,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n">
-        <v>1.42</v>
+      <c r="J21" s="3" t="n">
+        <v>1.35</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1539,8 +1539,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="3" t="n">
-        <v>1.32</v>
+      <c r="J22" s="4" t="n">
+        <v>1.42</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,43 +1638,43 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1686,8 +1686,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
-        <v>1.54</v>
+      <c r="J25" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1833,8 +1833,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="3" t="n">
-        <v>1.26</v>
+      <c r="J28" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1883,43 +1883,43 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2078,8 +2078,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J33" s="3" t="n">
-        <v>1.38</v>
+      <c r="J33" s="4" t="n">
+        <v>1.41</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2127,8 +2127,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J34" s="4" t="n">
-        <v>1.5</v>
+      <c r="J34" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2372,8 +2372,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J39" s="3" t="n">
-        <v>1.25</v>
+      <c r="J39" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2421,8 +2421,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J40" s="4" t="n">
-        <v>1.53</v>
+      <c r="J40" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2678,32 +2678,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="J46" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2727,32 +2727,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2764,7 +2764,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr"/>
+      <c r="J47" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2774,32 +2776,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2821,32 +2823,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2868,32 +2870,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2915,32 +2917,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2962,32 +2964,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3009,32 +3011,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3056,32 +3058,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3103,32 +3105,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3150,32 +3152,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3197,32 +3199,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3244,32 +3246,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3291,32 +3293,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3338,32 +3340,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3377,6 +3379,53 @@
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4162.96</v>
+        <v>4114.77</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$13.14</t>
+          <t>+$4.74</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4190.3</v>
+        <v>4140.7</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>27.34</v>
+        <v>25.93</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4129.15</v>
+        <v>4162.96</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$1.31</t>
+          <t>+$13.14</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4156.7</v>
+        <v>4190.3</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>27.55</v>
+        <v>27.34</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4139.21</v>
+        <v>4129.15</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>+$1.31</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4167.9</v>
+        <v>4156.7</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>28.69</v>
+        <v>27.55</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1196,8 +1196,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n">
-        <v>1.55</v>
+      <c r="J15" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,28 +1306,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1490,8 +1490,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J21" s="3" t="n">
-        <v>1.35</v>
+      <c r="J21" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1539,8 +1539,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="4" t="n">
-        <v>1.42</v>
+      <c r="J22" s="3" t="n">
+        <v>1.35</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1588,8 +1588,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="3" t="n">
-        <v>1.32</v>
+      <c r="J23" s="4" t="n">
+        <v>1.42</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,43 +1687,43 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1735,8 +1735,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>1.54</v>
+      <c r="J26" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1882,8 +1882,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="3" t="n">
-        <v>1.26</v>
+      <c r="J29" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1932,43 +1932,43 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2078,8 +2078,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n">
-        <v>1.41</v>
+      <c r="J33" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2127,8 +2127,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J34" s="3" t="n">
-        <v>1.38</v>
+      <c r="J34" s="4" t="n">
+        <v>1.41</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2176,8 +2176,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n">
-        <v>1.5</v>
+      <c r="J35" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2421,8 +2421,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J40" s="3" t="n">
-        <v>1.25</v>
+      <c r="J40" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2470,8 +2470,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J41" s="4" t="n">
-        <v>1.53</v>
+      <c r="J41" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2678,32 +2678,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="J46" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2727,32 +2727,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2813,7 +2813,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr"/>
+      <c r="J48" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2823,32 +2825,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2870,32 +2872,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2917,32 +2919,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2964,32 +2966,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3011,32 +3013,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3058,32 +3060,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3105,32 +3107,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3152,32 +3154,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3199,32 +3201,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3246,32 +3248,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3293,32 +3295,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3340,32 +3342,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3387,32 +3389,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3426,6 +3428,53 @@
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4114.77</v>
+        <v>4130.14</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$4.74</t>
+          <t>$-0.10</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4140.7</v>
+        <v>4154.6</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>25.93</v>
+        <v>24.46</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4162.96</v>
+        <v>4114.77</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$13.14</t>
+          <t>+$4.74</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4190.3</v>
+        <v>4140.7</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>27.34</v>
+        <v>25.93</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4129.15</v>
+        <v>4162.96</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$1.31</t>
+          <t>+$13.14</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4156.7</v>
+        <v>4190.3</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>27.55</v>
+        <v>27.34</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4139.21</v>
+        <v>4129.15</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>+$1.31</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4167.9</v>
+        <v>4156.7</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>28.69</v>
+        <v>27.55</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="J15" s="4" t="n">
         <v>1.38</v>
       </c>
       <c r="K15" t="inlineStr">
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,28 +1355,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1539,8 +1539,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="3" t="n">
-        <v>1.35</v>
+      <c r="J22" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1588,8 +1588,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n">
-        <v>1.42</v>
+      <c r="J23" s="3" t="n">
+        <v>1.35</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1637,8 +1637,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="3" t="n">
-        <v>1.32</v>
+      <c r="J24" s="4" t="n">
+        <v>1.42</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,43 +1736,43 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1784,8 +1784,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n">
-        <v>1.54</v>
+      <c r="J27" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1931,8 +1931,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="3" t="n">
-        <v>1.26</v>
+      <c r="J30" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1981,43 +1981,43 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2127,8 +2127,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J34" s="4" t="n">
-        <v>1.41</v>
+      <c r="J34" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2176,8 +2176,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J35" s="3" t="n">
-        <v>1.38</v>
+      <c r="J35" s="4" t="n">
+        <v>1.41</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J40" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2470,8 +2470,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J41" s="3" t="n">
-        <v>1.25</v>
+      <c r="J41" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2519,8 +2519,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J42" s="4" t="n">
-        <v>1.53</v>
+      <c r="J42" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2678,32 +2678,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="J46" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2727,32 +2727,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="J48" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2825,32 +2825,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2862,7 +2862,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr"/>
+      <c r="J49" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2872,32 +2874,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2919,32 +2921,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2966,32 +2968,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3013,32 +3015,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3060,32 +3062,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3107,32 +3109,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3154,32 +3156,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3201,32 +3203,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3248,32 +3250,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3295,32 +3297,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3342,32 +3344,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3389,32 +3391,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3436,32 +3438,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3475,6 +3477,53 @@
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4130.14</v>
+        <v>4191.2</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>$-0.10</t>
+          <t>$-6.33</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4154.6</v>
+        <v>4216.3</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+1.49%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>24.46</v>
+        <v>25.1</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4114.77</v>
+        <v>4130.14</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$4.74</t>
+          <t>$-0.10</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4140.7</v>
+        <v>4154.6</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>25.93</v>
+        <v>24.46</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4162.96</v>
+        <v>4114.77</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$13.14</t>
+          <t>+$4.74</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4190.3</v>
+        <v>4140.7</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>27.34</v>
+        <v>25.93</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4129.15</v>
+        <v>4162.96</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$1.31</t>
+          <t>+$13.14</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4156.7</v>
+        <v>4190.3</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>27.55</v>
+        <v>27.34</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4139.21</v>
+        <v>4129.15</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>+$1.31</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4167.9</v>
+        <v>4156.7</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>28.69</v>
+        <v>27.55</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1196,8 +1196,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n">
-        <v>1.38</v>
+      <c r="J15" s="3" t="n">
+        <v>1.27</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,28 +1404,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1588,8 +1588,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="3" t="n">
-        <v>1.35</v>
+      <c r="J23" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1637,8 +1637,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n">
-        <v>1.42</v>
+      <c r="J24" s="3" t="n">
+        <v>1.35</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1686,8 +1686,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="3" t="n">
-        <v>1.32</v>
+      <c r="J25" s="4" t="n">
+        <v>1.42</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,43 +1785,43 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1833,8 +1833,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n">
-        <v>1.54</v>
+      <c r="J28" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1980,8 +1980,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="3" t="n">
-        <v>1.26</v>
+      <c r="J31" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2030,43 +2030,43 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2176,8 +2176,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n">
-        <v>1.41</v>
+      <c r="J35" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2519,8 +2519,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J42" s="3" t="n">
-        <v>1.25</v>
+      <c r="J42" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2568,8 +2568,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J43" s="4" t="n">
-        <v>1.53</v>
+      <c r="J43" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2678,32 +2678,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="J46" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2727,32 +2727,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="J48" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2825,32 +2825,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2874,32 +2874,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2911,7 +2911,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr"/>
+      <c r="J50" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2921,32 +2923,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2968,32 +2970,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3015,32 +3017,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3062,32 +3064,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3109,32 +3111,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3156,32 +3158,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3203,32 +3205,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3250,32 +3252,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3297,32 +3299,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3344,32 +3346,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3391,32 +3393,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3438,32 +3440,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3485,32 +3487,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3524,6 +3526,53 @@
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>4167.55</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>+$2.52</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>4191.2</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>+1.48%</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>$-6.33</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4216.3</v>
-      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>25.1</v>
+        <v>23.65</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4130.14</v>
+        <v>4191.2</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>$-0.10</t>
+          <t>$-6.33</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4154.6</v>
+        <v>4216.3</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+1.49%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>24.46</v>
+        <v>25.1</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4114.77</v>
+        <v>4130.14</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$4.74</t>
+          <t>$-0.10</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4140.7</v>
+        <v>4154.6</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>25.93</v>
+        <v>24.46</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4162.96</v>
+        <v>4114.77</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$13.14</t>
+          <t>+$4.74</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4190.3</v>
+        <v>4140.7</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>27.34</v>
+        <v>25.93</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4129.15</v>
+        <v>4162.96</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$1.31</t>
+          <t>+$13.14</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4156.7</v>
+        <v>4190.3</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>27.55</v>
+        <v>27.34</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4139.21</v>
+        <v>4129.15</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>+$1.31</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4167.9</v>
+        <v>4156.7</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>28.69</v>
+        <v>27.55</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1245,8 +1245,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="4" t="n">
-        <v>1.38</v>
+      <c r="J16" s="3" t="n">
+        <v>1.27</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,28 +1453,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1637,8 +1637,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="3" t="n">
-        <v>1.35</v>
+      <c r="J24" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1686,8 +1686,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
-        <v>1.42</v>
+      <c r="J25" s="3" t="n">
+        <v>1.35</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1735,8 +1735,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="3" t="n">
-        <v>1.32</v>
+      <c r="J26" s="4" t="n">
+        <v>1.42</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1834,43 +1834,43 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1882,8 +1882,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n">
-        <v>1.54</v>
+      <c r="J29" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2029,8 +2029,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J32" s="3" t="n">
-        <v>1.26</v>
+      <c r="J32" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2079,43 +2079,43 @@
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2225,8 +2225,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J36" s="4" t="n">
-        <v>1.41</v>
+      <c r="J36" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J40" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2568,8 +2568,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J43" s="3" t="n">
-        <v>1.25</v>
+      <c r="J43" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2617,8 +2617,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J44" s="4" t="n">
-        <v>1.53</v>
+      <c r="J44" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2678,32 +2678,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="J46" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2727,32 +2727,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="J48" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2825,32 +2825,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2874,32 +2874,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="J50" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2923,32 +2923,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2960,7 +2960,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr"/>
+      <c r="J51" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -2970,32 +2972,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3017,32 +3019,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3064,32 +3066,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3111,32 +3113,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3158,32 +3160,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3205,32 +3207,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3252,32 +3254,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3299,32 +3301,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3346,32 +3348,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3393,32 +3395,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3440,32 +3442,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3487,32 +3489,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3534,32 +3536,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3573,6 +3575,53 @@
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4167.55</v>
+        <v>4154.9</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$2.52</t>
+          <t>+$6.19</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4191.2</v>
+        <v>4178.3</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>23.65</v>
+        <v>23.4</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>4167.55</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>+$2.52</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>4191.2</v>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>+1.48%</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>$-6.33</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>4216.3</v>
-      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>25.1</v>
+        <v>23.65</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4130.14</v>
+        <v>4191.2</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-0.10</t>
+          <t>$-6.33</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4154.6</v>
+        <v>4216.3</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+1.49%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>24.46</v>
+        <v>25.1</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4114.77</v>
+        <v>4130.14</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$4.74</t>
+          <t>$-0.10</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4140.7</v>
+        <v>4154.6</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>25.93</v>
+        <v>24.46</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4162.96</v>
+        <v>4114.77</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$13.14</t>
+          <t>+$4.74</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4190.3</v>
+        <v>4140.7</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>27.34</v>
+        <v>25.93</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4129.15</v>
+        <v>4162.96</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$1.31</t>
+          <t>+$13.14</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4156.7</v>
+        <v>4190.3</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>27.55</v>
+        <v>27.34</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4139.21</v>
+        <v>4129.15</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>+$1.31</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4167.9</v>
+        <v>4156.7</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>28.69</v>
+        <v>27.55</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1294,8 +1294,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n">
-        <v>1.38</v>
+      <c r="J17" s="3" t="n">
+        <v>1.27</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,28 +1502,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1686,8 +1686,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="3" t="n">
-        <v>1.35</v>
+      <c r="J25" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1735,8 +1735,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>1.42</v>
+      <c r="J26" s="3" t="n">
+        <v>1.35</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1784,8 +1784,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="3" t="n">
-        <v>1.32</v>
+      <c r="J27" s="4" t="n">
+        <v>1.42</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1883,43 +1883,43 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1931,8 +1931,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n">
-        <v>1.54</v>
+      <c r="J30" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2078,8 +2078,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J33" s="3" t="n">
-        <v>1.26</v>
+      <c r="J33" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2128,43 +2128,43 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2274,8 +2274,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J37" s="4" t="n">
-        <v>1.41</v>
+      <c r="J37" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J40" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2617,8 +2617,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J44" s="3" t="n">
-        <v>1.25</v>
+      <c r="J44" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2666,8 +2666,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J45" s="4" t="n">
-        <v>1.53</v>
+      <c r="J45" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2678,32 +2678,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="J46" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2727,32 +2727,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="J48" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2825,32 +2825,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2874,32 +2874,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="J50" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2923,32 +2923,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="J51" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2972,32 +2972,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3009,7 +3009,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr"/>
+      <c r="J52" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -3019,32 +3021,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3066,32 +3068,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3113,32 +3115,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3160,32 +3162,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3207,32 +3209,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3254,32 +3256,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3301,32 +3303,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3348,32 +3350,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3395,32 +3397,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3442,32 +3444,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3489,32 +3491,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3536,32 +3538,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3583,32 +3585,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3622,6 +3624,53 @@
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4154.9</v>
+        <v>4087.97</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$6.19</t>
+          <t>+$6.22</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4178.3</v>
+        <v>4109.8</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>23.4</v>
+        <v>21.83</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4167.55</v>
+        <v>4154.9</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$2.52</t>
+          <t>+$6.19</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4191.2</v>
+        <v>4178.3</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>23.65</v>
+        <v>23.4</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>4167.55</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>+$2.52</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>4191.2</v>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>+1.48%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>$-6.33</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>4216.3</v>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>25.1</v>
+        <v>23.65</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4130.14</v>
+        <v>4191.2</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-0.10</t>
+          <t>$-6.33</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4154.6</v>
+        <v>4216.3</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+1.49%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>24.46</v>
+        <v>25.1</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4114.77</v>
+        <v>4130.14</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$4.74</t>
+          <t>$-0.10</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4140.7</v>
+        <v>4154.6</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>25.93</v>
+        <v>24.46</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4162.96</v>
+        <v>4114.77</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$13.14</t>
+          <t>+$4.74</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4190.3</v>
+        <v>4140.7</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>27.34</v>
+        <v>25.93</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4129.15</v>
+        <v>4162.96</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$1.31</t>
+          <t>+$13.14</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4156.7</v>
+        <v>4190.3</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>27.55</v>
+        <v>27.34</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4139.21</v>
+        <v>4129.15</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>+$1.31</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4167.9</v>
+        <v>4156.7</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>28.69</v>
+        <v>27.55</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1343,8 +1343,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n">
-        <v>1.38</v>
+      <c r="J18" s="3" t="n">
+        <v>1.27</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,28 +1551,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1735,8 +1735,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="3" t="n">
-        <v>1.35</v>
+      <c r="J26" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1784,8 +1784,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n">
-        <v>1.42</v>
+      <c r="J27" s="3" t="n">
+        <v>1.35</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1833,8 +1833,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="3" t="n">
-        <v>1.32</v>
+      <c r="J28" s="4" t="n">
+        <v>1.42</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1932,43 +1932,43 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1980,8 +1980,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
-        <v>1.54</v>
+      <c r="J31" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2127,8 +2127,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J34" s="3" t="n">
-        <v>1.26</v>
+      <c r="J34" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2177,43 +2177,43 @@
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="J37" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2323,8 +2323,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J38" s="4" t="n">
-        <v>1.41</v>
+      <c r="J38" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J40" s="4" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2666,8 +2666,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J45" s="3" t="n">
-        <v>1.25</v>
+      <c r="J45" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2678,32 +2678,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2715,8 +2715,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J46" s="4" t="n">
-        <v>1.53</v>
+      <c r="J46" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2727,32 +2727,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="J48" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2825,32 +2825,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2874,32 +2874,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="J50" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2923,32 +2923,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="J51" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2972,32 +2972,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="J52" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3021,32 +3021,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3058,7 +3058,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr"/>
+      <c r="J53" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -3068,32 +3070,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3115,32 +3117,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3162,32 +3164,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3209,32 +3211,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3256,32 +3258,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3303,32 +3305,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3350,32 +3352,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3397,32 +3399,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3444,32 +3446,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3491,32 +3493,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3538,32 +3540,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3585,32 +3587,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3632,32 +3634,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3671,6 +3673,53 @@
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4087.97</v>
+        <v>4150.36</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.53%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$6.22</t>
+          <t>+$20.34</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4109.8</v>
+        <v>4171.5</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>21.83</v>
+        <v>21.14</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4154.9</v>
+        <v>4087.97</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$6.19</t>
+          <t>+$6.22</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4178.3</v>
+        <v>4109.8</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>23.4</v>
+        <v>21.83</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4167.55</v>
+        <v>4154.9</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$2.52</t>
+          <t>+$6.19</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4191.2</v>
+        <v>4178.3</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>23.65</v>
+        <v>23.4</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>4167.55</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>+$2.52</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>4191.2</v>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>+1.48%</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>$-6.33</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>4216.3</v>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>25.1</v>
+        <v>23.65</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4130.14</v>
+        <v>4191.2</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-0.10</t>
+          <t>$-6.33</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4154.6</v>
+        <v>4216.3</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+1.49%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>24.46</v>
+        <v>25.1</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4114.77</v>
+        <v>4130.14</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$4.74</t>
+          <t>$-0.10</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4140.7</v>
+        <v>4154.6</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>25.93</v>
+        <v>24.46</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4162.96</v>
+        <v>4114.77</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$13.14</t>
+          <t>+$4.74</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4190.3</v>
+        <v>4140.7</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>27.34</v>
+        <v>25.93</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4129.15</v>
+        <v>4162.96</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$1.31</t>
+          <t>+$13.14</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4156.7</v>
+        <v>4190.3</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>27.55</v>
+        <v>27.34</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4139.21</v>
+        <v>4129.15</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>+$1.31</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4167.9</v>
+        <v>4156.7</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>28.69</v>
+        <v>27.55</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1392,8 +1392,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n">
-        <v>1.38</v>
+      <c r="J19" s="3" t="n">
+        <v>1.27</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,28 +1600,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1784,8 +1784,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="3" t="n">
-        <v>1.35</v>
+      <c r="J27" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1833,8 +1833,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n">
-        <v>1.42</v>
+      <c r="J28" s="3" t="n">
+        <v>1.35</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1882,8 +1882,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="3" t="n">
-        <v>1.32</v>
+      <c r="J29" s="4" t="n">
+        <v>1.42</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1981,43 +1981,43 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2029,8 +2029,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J32" s="4" t="n">
-        <v>1.54</v>
+      <c r="J32" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2176,8 +2176,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J35" s="3" t="n">
-        <v>1.26</v>
+      <c r="J35" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2226,43 +2226,43 @@
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="J37" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2372,8 +2372,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J39" s="4" t="n">
-        <v>1.41</v>
+      <c r="J39" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J40" s="4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2678,32 +2678,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2715,8 +2715,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J46" s="3" t="n">
-        <v>1.25</v>
+      <c r="J46" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2727,32 +2727,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2764,8 +2764,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J47" s="4" t="n">
-        <v>1.53</v>
+      <c r="J47" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="J48" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2825,32 +2825,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2874,32 +2874,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="J50" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2923,32 +2923,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="J51" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2972,32 +2972,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="J52" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3021,32 +3021,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="J53" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3070,32 +3070,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3107,7 +3107,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="J54" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -3117,32 +3119,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3164,32 +3166,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3211,32 +3213,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3258,32 +3260,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3305,32 +3307,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3352,32 +3354,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3399,32 +3401,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3446,32 +3448,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3493,32 +3495,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3540,32 +3542,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3587,32 +3589,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3634,32 +3636,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3681,32 +3683,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3720,6 +3722,53 @@
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4150.36</v>
+        <v>4161.81</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$20.34</t>
+          <t>+$21.36</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4171.5</v>
+        <v>4182.2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>21.14</v>
+        <v>20.39</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.11</v>
+        <v>0.96</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4087.97</v>
+        <v>4150.36</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.53%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$6.22</t>
+          <t>+$20.34</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4109.8</v>
+        <v>4171.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>21.83</v>
+        <v>21.14</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4154.9</v>
+        <v>4087.97</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$6.19</t>
+          <t>+$6.22</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4178.3</v>
+        <v>4109.8</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>23.4</v>
+        <v>21.83</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4167.55</v>
+        <v>4154.9</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$2.52</t>
+          <t>+$6.19</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4191.2</v>
+        <v>4178.3</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>23.65</v>
+        <v>23.4</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>4167.55</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>+$2.52</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>4191.2</v>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>+1.48%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>$-6.33</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>4216.3</v>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>25.1</v>
+        <v>23.65</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4130.14</v>
+        <v>4191.2</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-0.10</t>
+          <t>$-6.33</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4154.6</v>
+        <v>4216.3</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+1.49%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>24.46</v>
+        <v>25.1</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4114.77</v>
+        <v>4130.14</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$4.74</t>
+          <t>$-0.10</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4140.7</v>
+        <v>4154.6</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>25.93</v>
+        <v>24.46</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4162.96</v>
+        <v>4114.77</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$13.14</t>
+          <t>+$4.74</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4190.3</v>
+        <v>4140.7</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>27.34</v>
+        <v>25.93</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4129.15</v>
+        <v>4162.96</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$1.31</t>
+          <t>+$13.14</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4156.7</v>
+        <v>4190.3</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>27.55</v>
+        <v>27.34</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4139.21</v>
+        <v>4129.15</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>+$1.31</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4167.9</v>
+        <v>4156.7</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>28.69</v>
+        <v>27.55</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1441,8 +1441,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n">
-        <v>1.38</v>
+      <c r="J20" s="3" t="n">
+        <v>1.27</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,28 +1649,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1833,8 +1833,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="3" t="n">
-        <v>1.35</v>
+      <c r="J28" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1882,8 +1882,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n">
-        <v>1.42</v>
+      <c r="J29" s="3" t="n">
+        <v>1.35</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1931,8 +1931,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="3" t="n">
-        <v>1.32</v>
+      <c r="J30" s="4" t="n">
+        <v>1.42</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2030,43 +2030,43 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2078,8 +2078,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n">
-        <v>1.54</v>
+      <c r="J33" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2225,8 +2225,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J36" s="3" t="n">
-        <v>1.26</v>
+      <c r="J36" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,43 +2275,43 @@
         </is>
       </c>
       <c r="J37" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="J39" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2421,8 +2421,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J40" s="4" t="n">
-        <v>1.41</v>
+      <c r="J40" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2678,32 +2678,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="J46" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2727,32 +2727,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2764,8 +2764,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J47" s="3" t="n">
-        <v>1.25</v>
+      <c r="J47" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2813,8 +2813,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J48" s="4" t="n">
-        <v>1.53</v>
+      <c r="J48" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2825,32 +2825,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2874,32 +2874,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="J50" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2923,32 +2923,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="J51" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2972,32 +2972,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="J52" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3021,32 +3021,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="J53" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3070,32 +3070,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="J54" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3119,32 +3119,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3156,7 +3156,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr"/>
+      <c r="J55" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -3166,32 +3168,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3213,32 +3215,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3260,32 +3262,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3307,32 +3309,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3354,32 +3356,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3401,32 +3403,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3448,32 +3450,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3495,32 +3497,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3542,32 +3544,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3589,32 +3591,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3636,32 +3638,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3683,32 +3685,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3730,32 +3732,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3769,6 +3771,53 @@
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4161.81</v>
+        <v>4143.83</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$21.36</t>
+          <t>$-1.16</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4182.2</v>
+        <v>4163.1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>20.39</v>
+        <v>19.27</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4150.36</v>
+        <v>4161.81</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$20.34</t>
+          <t>+$21.36</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4171.5</v>
+        <v>4182.2</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>21.14</v>
+        <v>20.39</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.11</v>
+        <v>0.96</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4087.97</v>
+        <v>4150.36</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.53%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$6.22</t>
+          <t>+$20.34</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4109.8</v>
+        <v>4171.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>21.83</v>
+        <v>21.14</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4154.9</v>
+        <v>4087.97</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$6.19</t>
+          <t>+$6.22</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4178.3</v>
+        <v>4109.8</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>23.4</v>
+        <v>21.83</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4167.55</v>
+        <v>4154.9</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$2.52</t>
+          <t>+$6.19</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4191.2</v>
+        <v>4178.3</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>23.65</v>
+        <v>23.4</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>4167.55</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>+$2.52</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>4191.2</v>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>+1.48%</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>$-6.33</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>4216.3</v>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>25.1</v>
+        <v>23.65</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4130.14</v>
+        <v>4191.2</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-0.10</t>
+          <t>$-6.33</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4154.6</v>
+        <v>4216.3</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+1.49%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>24.46</v>
+        <v>25.1</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4114.77</v>
+        <v>4130.14</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$4.74</t>
+          <t>$-0.10</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4140.7</v>
+        <v>4154.6</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>25.93</v>
+        <v>24.46</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4162.96</v>
+        <v>4114.77</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$13.14</t>
+          <t>+$4.74</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4190.3</v>
+        <v>4140.7</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>27.34</v>
+        <v>25.93</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4129.15</v>
+        <v>4162.96</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$1.31</t>
+          <t>+$13.14</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4156.7</v>
+        <v>4190.3</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>27.55</v>
+        <v>27.34</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4139.21</v>
+        <v>4129.15</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>+$1.31</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4167.9</v>
+        <v>4156.7</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>28.69</v>
+        <v>27.55</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1490,8 +1490,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n">
-        <v>1.38</v>
+      <c r="J21" s="3" t="n">
+        <v>1.27</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,28 +1698,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1882,8 +1882,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="3" t="n">
-        <v>1.35</v>
+      <c r="J29" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1931,8 +1931,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n">
-        <v>1.42</v>
+      <c r="J30" s="3" t="n">
+        <v>1.35</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1980,8 +1980,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="3" t="n">
-        <v>1.32</v>
+      <c r="J31" s="4" t="n">
+        <v>1.42</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2079,43 +2079,43 @@
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2127,8 +2127,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J34" s="4" t="n">
-        <v>1.54</v>
+      <c r="J34" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2274,8 +2274,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J37" s="3" t="n">
-        <v>1.26</v>
+      <c r="J37" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,43 +2324,43 @@
         </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="J39" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J40" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2470,8 +2470,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J41" s="4" t="n">
-        <v>1.41</v>
+      <c r="J41" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2678,32 +2678,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2727,32 +2727,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2813,8 +2813,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J48" s="3" t="n">
-        <v>1.25</v>
+      <c r="J48" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2825,32 +2825,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2862,8 +2862,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J49" s="4" t="n">
-        <v>1.53</v>
+      <c r="J49" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2874,32 +2874,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="J50" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2923,32 +2923,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="J51" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2972,32 +2972,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="J52" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3021,32 +3021,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="J53" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3070,32 +3070,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="J54" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3119,32 +3119,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3168,32 +3168,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3205,7 +3205,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr"/>
+      <c r="J56" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -3215,32 +3217,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3262,32 +3264,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3309,32 +3311,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3356,32 +3358,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3403,32 +3405,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3450,32 +3452,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3497,32 +3499,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3544,32 +3546,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3591,32 +3593,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3638,32 +3640,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3685,32 +3687,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3732,32 +3734,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3779,32 +3781,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3818,6 +3820,53 @@
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4143.83</v>
+        <v>4123.8</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>$-1.16</t>
+          <t>+$2.14</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4163.1</v>
+        <v>4142.6</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>19.27</v>
+        <v>18.8</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4161.81</v>
+        <v>4143.83</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$21.36</t>
+          <t>$-1.16</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4182.2</v>
+        <v>4163.1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>20.39</v>
+        <v>19.27</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4150.36</v>
+        <v>4161.81</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$20.34</t>
+          <t>+$21.36</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4171.5</v>
+        <v>4182.2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>21.14</v>
+        <v>20.39</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.11</v>
+        <v>0.96</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4087.97</v>
+        <v>4150.36</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.53%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$6.22</t>
+          <t>+$20.34</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4109.8</v>
+        <v>4171.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>21.83</v>
+        <v>21.14</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4154.9</v>
+        <v>4087.97</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$6.19</t>
+          <t>+$6.22</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4178.3</v>
+        <v>4109.8</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>23.4</v>
+        <v>21.83</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4167.55</v>
+        <v>4154.9</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$2.52</t>
+          <t>+$6.19</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4191.2</v>
+        <v>4178.3</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>23.65</v>
+        <v>23.4</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>4167.55</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>+$2.52</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>4191.2</v>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>+1.48%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>$-6.33</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>4216.3</v>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>25.1</v>
+        <v>23.65</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4130.14</v>
+        <v>4191.2</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-0.10</t>
+          <t>$-6.33</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4154.6</v>
+        <v>4216.3</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+1.49%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>24.46</v>
+        <v>25.1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4114.77</v>
+        <v>4130.14</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$4.74</t>
+          <t>$-0.10</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4140.7</v>
+        <v>4154.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>25.93</v>
+        <v>24.46</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4162.96</v>
+        <v>4114.77</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$13.14</t>
+          <t>+$4.74</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4190.3</v>
+        <v>4140.7</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>27.34</v>
+        <v>25.93</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4129.15</v>
+        <v>4162.96</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$1.31</t>
+          <t>+$13.14</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4156.7</v>
+        <v>4190.3</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>27.55</v>
+        <v>27.34</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4139.21</v>
+        <v>4129.15</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>+$1.31</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4167.9</v>
+        <v>4156.7</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>28.69</v>
+        <v>27.55</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1539,8 +1539,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="4" t="n">
-        <v>1.38</v>
+      <c r="J22" s="3" t="n">
+        <v>1.27</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,28 +1747,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1931,8 +1931,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="3" t="n">
-        <v>1.35</v>
+      <c r="J30" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1980,8 +1980,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
-        <v>1.42</v>
+      <c r="J31" s="3" t="n">
+        <v>1.35</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2029,8 +2029,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J32" s="3" t="n">
-        <v>1.32</v>
+      <c r="J32" s="4" t="n">
+        <v>1.42</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2128,43 +2128,43 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2323,8 +2323,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J38" s="3" t="n">
-        <v>1.26</v>
+      <c r="J38" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2373,43 +2373,43 @@
         </is>
       </c>
       <c r="J39" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J40" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="J41" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2678,32 +2678,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="J46" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2727,32 +2727,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="J48" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2825,32 +2825,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2862,8 +2862,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J49" s="3" t="n">
-        <v>1.25</v>
+      <c r="J49" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2874,32 +2874,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2911,8 +2911,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J50" s="4" t="n">
-        <v>1.53</v>
+      <c r="J50" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2923,32 +2923,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="J51" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2972,32 +2972,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="J52" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3021,32 +3021,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="J53" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3070,32 +3070,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="J54" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3119,32 +3119,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3168,32 +3168,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="J56" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3217,32 +3217,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3254,7 +3254,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr"/>
+      <c r="J57" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -3264,32 +3266,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3311,32 +3313,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3358,32 +3360,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3405,32 +3407,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3452,32 +3454,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3499,32 +3501,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3546,32 +3548,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3593,32 +3595,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3640,32 +3642,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3687,32 +3689,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3734,32 +3736,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3781,32 +3783,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3828,32 +3830,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3867,6 +3869,53 @@
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4123.8</v>
+        <v>4132.95</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$2.14</t>
+          <t>+$3.15</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4142.6</v>
+        <v>4151.2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>18.8</v>
+        <v>18.25</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4143.83</v>
+        <v>4123.8</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>$-1.16</t>
+          <t>+$2.14</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4163.1</v>
+        <v>4142.6</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>19.27</v>
+        <v>18.8</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4161.81</v>
+        <v>4143.83</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$21.36</t>
+          <t>$-1.16</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4182.2</v>
+        <v>4163.1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>20.39</v>
+        <v>19.27</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4150.36</v>
+        <v>4161.81</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$20.34</t>
+          <t>+$21.36</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4171.5</v>
+        <v>4182.2</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>21.14</v>
+        <v>20.39</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.11</v>
+        <v>0.96</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4087.97</v>
+        <v>4150.36</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.53%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$6.22</t>
+          <t>+$20.34</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4109.8</v>
+        <v>4171.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>21.83</v>
+        <v>21.14</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4154.9</v>
+        <v>4087.97</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$6.19</t>
+          <t>+$6.22</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4178.3</v>
+        <v>4109.8</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>23.4</v>
+        <v>21.83</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4167.55</v>
+        <v>4154.9</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$2.52</t>
+          <t>+$6.19</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4191.2</v>
+        <v>4178.3</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>23.65</v>
+        <v>23.4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>4167.55</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>+$2.52</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>4191.2</v>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>+1.48%</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>$-6.33</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>4216.3</v>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>25.1</v>
+        <v>23.65</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4130.14</v>
+        <v>4191.2</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-0.10</t>
+          <t>$-6.33</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4154.6</v>
+        <v>4216.3</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+1.49%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>24.46</v>
+        <v>25.1</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4114.77</v>
+        <v>4130.14</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$4.74</t>
+          <t>$-0.10</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4140.7</v>
+        <v>4154.6</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>25.93</v>
+        <v>24.46</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4162.96</v>
+        <v>4114.77</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$13.14</t>
+          <t>+$4.74</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4190.3</v>
+        <v>4140.7</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>27.34</v>
+        <v>25.93</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4129.15</v>
+        <v>4162.96</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$1.31</t>
+          <t>+$13.14</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4156.7</v>
+        <v>4190.3</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>27.55</v>
+        <v>27.34</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4139.21</v>
+        <v>4129.15</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>+$1.31</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4167.9</v>
+        <v>4156.7</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>28.69</v>
+        <v>27.55</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1588,8 +1588,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n">
-        <v>1.38</v>
+      <c r="J23" s="3" t="n">
+        <v>1.27</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,28 +1796,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1980,8 +1980,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="3" t="n">
-        <v>1.35</v>
+      <c r="J31" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2029,8 +2029,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J32" s="4" t="n">
-        <v>1.42</v>
+      <c r="J32" s="3" t="n">
+        <v>1.35</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2078,8 +2078,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J33" s="3" t="n">
-        <v>1.32</v>
+      <c r="J33" s="4" t="n">
+        <v>1.42</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2176,44 +2176,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n">
-        <v>1.37</v>
+      <c r="J35" s="3" t="n">
+        <v>1.34</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2372,8 +2372,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J39" s="3" t="n">
-        <v>1.26</v>
+      <c r="J39" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2422,43 +2422,43 @@
         </is>
       </c>
       <c r="J40" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="J41" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2519,8 +2519,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J42" s="4" t="n">
-        <v>1.37</v>
+      <c r="J42" s="3" t="n">
+        <v>1.19</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2678,32 +2678,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="J46" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2727,32 +2727,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2825,32 +2825,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2874,32 +2874,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2911,8 +2911,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J50" s="3" t="n">
-        <v>1.25</v>
+      <c r="J50" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2923,32 +2923,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2960,8 +2960,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J51" s="4" t="n">
-        <v>1.53</v>
+      <c r="J51" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2972,32 +2972,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="J52" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3021,32 +3021,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="J53" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3070,32 +3070,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="J54" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3119,32 +3119,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3168,32 +3168,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="J56" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3217,32 +3217,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="J57" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -3266,32 +3266,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3303,7 +3303,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr"/>
+      <c r="J58" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -3313,32 +3315,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3360,32 +3362,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3407,32 +3409,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3454,32 +3456,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3501,32 +3503,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3548,32 +3550,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3595,32 +3597,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3642,32 +3644,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3689,32 +3691,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3736,32 +3738,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3783,32 +3785,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3830,32 +3832,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3877,32 +3879,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3916,6 +3918,53 @@
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4132.95</v>
+        <v>4044.48</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-2.14%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$3.15</t>
+          <t>+$9.84</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4151.2</v>
+        <v>4060.1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-2.19%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>18.25</v>
+        <v>15.62</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4123.8</v>
+        <v>4132.95</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$2.14</t>
+          <t>+$3.15</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4142.6</v>
+        <v>4151.2</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>18.8</v>
+        <v>18.25</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4143.83</v>
+        <v>4123.8</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-1.16</t>
+          <t>+$2.14</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4163.1</v>
+        <v>4142.6</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>19.27</v>
+        <v>18.8</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4161.81</v>
+        <v>4143.83</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$21.36</t>
+          <t>$-1.16</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4182.2</v>
+        <v>4163.1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>20.39</v>
+        <v>19.27</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4150.36</v>
+        <v>4161.81</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$20.34</t>
+          <t>+$21.36</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4171.5</v>
+        <v>4182.2</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>21.14</v>
+        <v>20.39</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.11</v>
+        <v>0.96</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4087.97</v>
+        <v>4150.36</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.53%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$6.22</t>
+          <t>+$20.34</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4109.8</v>
+        <v>4171.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>21.83</v>
+        <v>21.14</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4154.9</v>
+        <v>4087.97</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$6.19</t>
+          <t>+$6.22</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4178.3</v>
+        <v>4109.8</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>23.4</v>
+        <v>21.83</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4167.55</v>
+        <v>4154.9</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$2.52</t>
+          <t>+$6.19</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4191.2</v>
+        <v>4178.3</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>23.65</v>
+        <v>23.4</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>4167.55</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>+$2.52</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
         <v>4191.2</v>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>+1.48%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>$-6.33</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>4216.3</v>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>25.1</v>
+        <v>23.65</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4130.14</v>
+        <v>4191.2</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-0.10</t>
+          <t>$-6.33</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4154.6</v>
+        <v>4216.3</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+1.49%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>24.46</v>
+        <v>25.1</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4114.77</v>
+        <v>4130.14</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$4.74</t>
+          <t>$-0.10</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4140.7</v>
+        <v>4154.6</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>25.93</v>
+        <v>24.46</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4162.96</v>
+        <v>4114.77</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$13.14</t>
+          <t>+$4.74</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4190.3</v>
+        <v>4140.7</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>27.34</v>
+        <v>25.93</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4129.15</v>
+        <v>4162.96</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$1.31</t>
+          <t>+$13.14</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4156.7</v>
+        <v>4190.3</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>27.55</v>
+        <v>27.34</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4139.21</v>
+        <v>4129.15</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>+$1.31</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4167.9</v>
+        <v>4156.7</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>28.69</v>
+        <v>27.55</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1637,8 +1637,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n">
-        <v>1.38</v>
+      <c r="J24" s="3" t="n">
+        <v>1.27</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2029,8 +2029,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J32" s="3" t="n">
-        <v>1.35</v>
+      <c r="J32" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2127,8 +2127,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J34" s="3" t="n">
-        <v>1.32</v>
+      <c r="J34" s="4" t="n">
+        <v>1.42</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2225,44 +2225,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J36" s="4" t="n">
-        <v>1.37</v>
+      <c r="J36" s="3" t="n">
+        <v>1.34</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2421,8 +2421,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J40" s="3" t="n">
-        <v>1.26</v>
+      <c r="J40" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2471,43 +2471,43 @@
         </is>
       </c>
       <c r="J41" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="J42" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2568,8 +2568,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J43" s="4" t="n">
-        <v>1.37</v>
+      <c r="J43" s="3" t="n">
+        <v>1.19</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2678,32 +2678,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="J46" s="4" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2727,32 +2727,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="J48" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2825,32 +2825,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2874,32 +2874,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="J50" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2923,32 +2923,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2960,8 +2960,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J51" s="3" t="n">
-        <v>1.25</v>
+      <c r="J51" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2972,32 +2972,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3009,8 +3009,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J52" s="4" t="n">
-        <v>1.53</v>
+      <c r="J52" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3021,32 +3021,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="J53" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3070,32 +3070,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="J54" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3119,32 +3119,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3168,32 +3168,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="J56" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3217,32 +3217,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="J57" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -3266,32 +3266,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="J58" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3315,32 +3315,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3352,7 +3352,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr"/>
+      <c r="J59" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -3362,32 +3364,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3409,32 +3411,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3456,32 +3458,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3503,32 +3505,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3550,32 +3552,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3597,32 +3599,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3644,32 +3646,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3691,32 +3693,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3738,32 +3740,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3785,32 +3787,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3832,32 +3834,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3879,32 +3881,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3926,32 +3928,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3965,6 +3967,53 @@
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4044.48</v>
+        <v>3996.05</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$9.84</t>
+          <t>$-18.26</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4060.1</v>
+        <v>4010</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>15.62</v>
+        <v>13.95</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4132.95</v>
+        <v>4044.48</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-2.14%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$3.15</t>
+          <t>+$9.84</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4151.2</v>
+        <v>4060.1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-2.19%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>18.25</v>
+        <v>15.62</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4123.8</v>
+        <v>4132.95</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$2.14</t>
+          <t>+$3.15</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4142.6</v>
+        <v>4151.2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>18.8</v>
+        <v>18.25</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4143.83</v>
+        <v>4123.8</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-1.16</t>
+          <t>+$2.14</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4163.1</v>
+        <v>4142.6</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>19.27</v>
+        <v>18.8</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4161.81</v>
+        <v>4143.83</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$21.36</t>
+          <t>$-1.16</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4182.2</v>
+        <v>4163.1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>20.39</v>
+        <v>19.27</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4150.36</v>
+        <v>4161.81</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$20.34</t>
+          <t>+$21.36</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4171.5</v>
+        <v>4182.2</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>21.14</v>
+        <v>20.39</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.11</v>
+        <v>0.96</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4087.97</v>
+        <v>4150.36</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.53%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$6.22</t>
+          <t>+$20.34</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4109.8</v>
+        <v>4171.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>21.83</v>
+        <v>21.14</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4154.9</v>
+        <v>4087.97</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$6.19</t>
+          <t>+$6.22</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4178.3</v>
+        <v>4109.8</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>23.4</v>
+        <v>21.83</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4167.55</v>
+        <v>4154.9</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$2.52</t>
+          <t>+$6.19</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4191.2</v>
+        <v>4178.3</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>23.65</v>
+        <v>23.4</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>4167.55</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>+$2.52</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
         <v>4191.2</v>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>+1.48%</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>$-6.33</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>4216.3</v>
-      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>25.1</v>
+        <v>23.65</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4130.14</v>
+        <v>4191.2</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-0.10</t>
+          <t>$-6.33</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4154.6</v>
+        <v>4216.3</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+1.49%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>24.46</v>
+        <v>25.1</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4114.77</v>
+        <v>4130.14</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$4.74</t>
+          <t>$-0.10</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4140.7</v>
+        <v>4154.6</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>25.93</v>
+        <v>24.46</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4162.96</v>
+        <v>4114.77</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$13.14</t>
+          <t>+$4.74</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4190.3</v>
+        <v>4140.7</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>27.34</v>
+        <v>25.93</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4129.15</v>
+        <v>4162.96</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$1.31</t>
+          <t>+$13.14</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4156.7</v>
+        <v>4190.3</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>27.55</v>
+        <v>27.34</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4139.21</v>
+        <v>4129.15</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>+$1.31</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4167.9</v>
+        <v>4156.7</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>28.69</v>
+        <v>27.55</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1686,8 +1686,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
-        <v>1.38</v>
+      <c r="J25" s="3" t="n">
+        <v>1.27</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,28 +1894,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2176,8 +2176,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J35" s="3" t="n">
-        <v>1.32</v>
+      <c r="J35" s="4" t="n">
+        <v>1.42</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,43 +2275,43 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J40" s="4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2470,8 +2470,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J41" s="3" t="n">
-        <v>1.26</v>
+      <c r="J41" s="4" t="n">
+        <v>1.47</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2520,43 +2520,43 @@
         </is>
       </c>
       <c r="J42" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="J43" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2617,8 +2617,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J44" s="4" t="n">
-        <v>1.37</v>
+      <c r="J44" s="3" t="n">
+        <v>1.19</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2678,32 +2678,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="J46" s="4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2727,32 +2727,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="J48" s="4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2825,32 +2825,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2874,32 +2874,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2923,32 +2923,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="J51" s="4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2972,32 +2972,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3009,8 +3009,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J52" s="3" t="n">
-        <v>1.25</v>
+      <c r="J52" s="4" t="n">
+        <v>1.49</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3021,32 +3021,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3058,8 +3058,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J53" s="4" t="n">
-        <v>1.53</v>
+      <c r="J53" s="3" t="n">
+        <v>1.25</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3070,32 +3070,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="J54" s="4" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3119,32 +3119,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3168,32 +3168,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="J56" s="4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3217,32 +3217,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="J57" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -3266,32 +3266,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="J58" s="4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3315,32 +3315,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="J59" s="4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -3364,32 +3364,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3401,7 +3401,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr"/>
+      <c r="J60" s="4" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -3411,32 +3413,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3458,32 +3460,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3505,32 +3507,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3552,32 +3554,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3599,32 +3601,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3646,32 +3648,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3693,32 +3695,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3740,32 +3742,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3787,32 +3789,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3834,32 +3836,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3881,32 +3883,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3928,32 +3930,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3975,32 +3977,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -4014,6 +4016,53 @@
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -38,14 +38,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3996.05</v>
+        <v>4015.69</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>$-18.26</t>
+          <t>+$2.20</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4010</v>
+        <v>4038.2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>13.95</v>
+        <v>22.51</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.06</v>
+        <v>1.66</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4044.48</v>
+        <v>3996.05</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$9.84</t>
+          <t>$-18.26</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4060.1</v>
+        <v>4010</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>15.62</v>
+        <v>13.95</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -608,8 +608,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>1.02</v>
+      <c r="J3" s="4" t="n">
+        <v>1.06</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4132.95</v>
+        <v>4044.48</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-2.14%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$3.15</t>
+          <t>+$9.84</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4151.2</v>
+        <v>4060.1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-2.19%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>18.25</v>
+        <v>15.62</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -657,8 +657,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>0.99</v>
+      <c r="J4" s="4" t="n">
+        <v>1.02</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4123.8</v>
+        <v>4132.95</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$2.14</t>
+          <t>+$3.15</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4142.6</v>
+        <v>4151.2</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>18.8</v>
+        <v>18.25</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -706,8 +706,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>0.96</v>
+      <c r="J5" s="4" t="n">
+        <v>0.99</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4143.83</v>
+        <v>4123.8</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-1.16</t>
+          <t>+$2.14</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4163.1</v>
+        <v>4142.6</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>19.27</v>
+        <v>18.8</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -755,8 +755,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>1.02</v>
+      <c r="J6" s="4" t="n">
+        <v>0.96</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4161.81</v>
+        <v>4143.83</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$21.36</t>
+          <t>$-1.16</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4182.2</v>
+        <v>4163.1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>20.39</v>
+        <v>19.27</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -804,8 +804,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n">
-        <v>0.96</v>
+      <c r="J7" s="4" t="n">
+        <v>1.02</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4150.36</v>
+        <v>4161.81</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$20.34</t>
+          <t>+$21.36</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4171.5</v>
+        <v>4182.2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>21.14</v>
+        <v>20.39</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -853,8 +853,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n">
-        <v>1.11</v>
+      <c r="J8" s="4" t="n">
+        <v>0.96</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4087.97</v>
+        <v>4150.36</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.53%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$6.22</t>
+          <t>+$20.34</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4109.8</v>
+        <v>4171.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>21.83</v>
+        <v>21.14</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -902,8 +902,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="3" t="n">
-        <v>1.06</v>
+      <c r="J9" s="4" t="n">
+        <v>1.11</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4154.9</v>
+        <v>4087.97</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$6.19</t>
+          <t>+$6.22</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4178.3</v>
+        <v>4109.8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>23.4</v>
+        <v>21.83</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -951,8 +951,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="3" t="n">
-        <v>1.02</v>
+      <c r="J10" s="4" t="n">
+        <v>1.06</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4167.55</v>
+        <v>4154.9</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$2.52</t>
+          <t>+$6.19</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4191.2</v>
+        <v>4178.3</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>23.65</v>
+        <v>23.4</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1000,8 +1000,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="3" t="n">
-        <v>1.13</v>
+      <c r="J11" s="4" t="n">
+        <v>1.02</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>4167.55</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>+$2.52</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>4191.2</v>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>+1.48%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>$-6.33</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>4216.3</v>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>25.1</v>
+        <v>23.65</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1049,8 +1049,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="3" t="n">
-        <v>1.03</v>
+      <c r="J12" s="4" t="n">
+        <v>1.13</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4130.14</v>
+        <v>4191.2</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-0.10</t>
+          <t>$-6.33</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4154.6</v>
+        <v>4216.3</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+1.49%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>24.46</v>
+        <v>25.1</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="J13" s="4" t="n">
         <v>1.03</v>
       </c>
       <c r="K13" t="inlineStr">
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4114.77</v>
+        <v>4130.14</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$4.74</t>
+          <t>$-0.10</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4140.7</v>
+        <v>4154.6</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>25.93</v>
+        <v>24.46</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1147,8 +1147,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>0.99</v>
+      <c r="J14" s="4" t="n">
+        <v>1.03</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4162.96</v>
+        <v>4114.77</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$13.14</t>
+          <t>+$4.74</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4190.3</v>
+        <v>4140.7</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>27.34</v>
+        <v>25.93</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1196,8 +1196,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="3" t="n">
-        <v>1.06</v>
+      <c r="J15" s="4" t="n">
+        <v>0.99</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4129.15</v>
+        <v>4162.96</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$1.31</t>
+          <t>+$13.14</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4156.7</v>
+        <v>4190.3</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>27.55</v>
+        <v>27.34</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1245,8 +1245,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="3" t="n">
-        <v>1.14</v>
+      <c r="J16" s="4" t="n">
+        <v>1.06</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4139.21</v>
+        <v>4129.15</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>+$1.31</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4167.9</v>
+        <v>4156.7</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>28.69</v>
+        <v>27.55</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1294,8 +1294,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="3" t="n">
-        <v>1.05</v>
+      <c r="J17" s="4" t="n">
+        <v>1.14</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1343,8 +1343,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J18" s="3" t="n">
-        <v>1.03</v>
+      <c r="J18" s="4" t="n">
+        <v>1.05</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1392,8 +1392,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="3" t="n">
-        <v>1.1</v>
+      <c r="J19" s="4" t="n">
+        <v>1.03</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1441,8 +1441,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="3" t="n">
-        <v>1.26</v>
+      <c r="J20" s="4" t="n">
+        <v>1.1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1490,8 +1490,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J21" s="3" t="n">
-        <v>1.29</v>
+      <c r="J21" s="4" t="n">
+        <v>1.26</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1539,8 +1539,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="3" t="n">
-        <v>1.3</v>
+      <c r="J22" s="4" t="n">
+        <v>1.29</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1588,8 +1588,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="3" t="n">
-        <v>1.31</v>
+      <c r="J23" s="4" t="n">
+        <v>1.3</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1637,8 +1637,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="3" t="n">
-        <v>1.29</v>
+      <c r="J24" s="4" t="n">
+        <v>1.31</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1686,8 +1686,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="3" t="n">
-        <v>1.27</v>
+      <c r="J25" s="4" t="n">
+        <v>1.29</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="J27" s="3" t="n">
         <v>1.38</v>
       </c>
       <c r="K27" t="inlineStr">
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1833,8 +1833,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n">
-        <v>1.55</v>
+      <c r="J28" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1882,8 +1882,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n">
-        <v>1.49</v>
+      <c r="J29" s="3" t="n">
+        <v>1.55</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1931,8 +1931,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n">
-        <v>1.56</v>
+      <c r="J30" s="3" t="n">
+        <v>1.49</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,28 +1943,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1980,8 +1980,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
-        <v>1.6</v>
+      <c r="J31" s="3" t="n">
+        <v>1.56</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2029,8 +2029,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J32" s="4" t="n">
-        <v>1.53</v>
+      <c r="J32" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2078,8 +2078,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n">
-        <v>1.54</v>
+      <c r="J33" s="3" t="n">
+        <v>1.53</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2127,8 +2127,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J34" s="4" t="n">
-        <v>1.35</v>
+      <c r="J34" s="3" t="n">
+        <v>1.54</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2176,8 +2176,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n">
-        <v>1.42</v>
+      <c r="J35" s="3" t="n">
+        <v>1.35</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,43 +2324,43 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2372,8 +2372,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J39" s="4" t="n">
-        <v>1.54</v>
+      <c r="J39" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2421,8 +2421,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J40" s="4" t="n">
-        <v>1.5</v>
+      <c r="J40" s="3" t="n">
+        <v>1.54</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2470,8 +2470,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J41" s="4" t="n">
-        <v>1.47</v>
+      <c r="J41" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="J42" s="3" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2568,44 +2568,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J43" s="3" t="n">
-        <v>1.22</v>
+      <c r="J43" s="4" t="n">
+        <v>1.26</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2617,8 +2617,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J44" s="3" t="n">
-        <v>1.19</v>
+      <c r="J44" s="4" t="n">
+        <v>1.22</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2678,32 +2678,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2715,8 +2715,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J46" s="4" t="n">
-        <v>1.41</v>
+      <c r="J46" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2727,32 +2727,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2764,8 +2764,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J47" s="4" t="n">
-        <v>1.38</v>
+      <c r="J47" s="3" t="n">
+        <v>1.41</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2813,8 +2813,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J48" s="4" t="n">
-        <v>1.5</v>
+      <c r="J48" s="3" t="n">
+        <v>1.38</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2825,32 +2825,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2862,8 +2862,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J49" s="4" t="n">
-        <v>1.45</v>
+      <c r="J49" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2874,32 +2874,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2911,8 +2911,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J50" s="4" t="n">
-        <v>1.52</v>
+      <c r="J50" s="3" t="n">
+        <v>1.45</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2923,32 +2923,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J51" s="4" t="n">
+      <c r="J51" s="3" t="n">
         <v>1.52</v>
       </c>
       <c r="K51" t="inlineStr">
@@ -2972,32 +2972,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3009,8 +3009,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J52" s="4" t="n">
-        <v>1.49</v>
+      <c r="J52" s="3" t="n">
+        <v>1.52</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3021,32 +3021,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="J53" s="3" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3070,32 +3070,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="J54" s="4" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3119,32 +3119,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3156,8 +3156,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J55" s="4" t="n">
-        <v>1.84</v>
+      <c r="J55" s="3" t="n">
+        <v>1.53</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3168,32 +3168,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3205,8 +3205,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J56" s="4" t="n">
-        <v>1.83</v>
+      <c r="J56" s="3" t="n">
+        <v>1.84</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3217,32 +3217,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3254,8 +3254,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J57" s="4" t="n">
-        <v>1.77</v>
+      <c r="J57" s="3" t="n">
+        <v>1.83</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -3266,32 +3266,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3303,8 +3303,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J58" s="4" t="n">
-        <v>1.64</v>
+      <c r="J58" s="3" t="n">
+        <v>1.77</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3315,32 +3315,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3352,8 +3352,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J59" s="4" t="n">
-        <v>1.71</v>
+      <c r="J59" s="3" t="n">
+        <v>1.64</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -3364,32 +3364,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3401,8 +3401,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J60" s="4" t="n">
-        <v>1.63</v>
+      <c r="J60" s="3" t="n">
+        <v>1.71</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -3413,32 +3413,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3450,7 +3450,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr"/>
+      <c r="J61" s="3" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -3460,32 +3462,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3507,32 +3509,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3554,32 +3556,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3601,32 +3603,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3648,32 +3650,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3695,32 +3697,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3742,32 +3744,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3789,32 +3791,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3836,32 +3838,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3883,32 +3885,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3930,32 +3932,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3977,32 +3979,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -4024,32 +4026,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -4063,6 +4065,53 @@
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4015.69</v>
+        <v>4056.06</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$2.20</t>
+          <t>+$2.81</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4038.2</v>
+        <v>4078.3</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>22.51</v>
+        <v>22.24</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3996.05</v>
+        <v>4015.69</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>$-18.26</t>
+          <t>+$2.20</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4010</v>
+        <v>4038.2</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>13.95</v>
+        <v>22.51</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -608,8 +608,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>1.06</v>
+      <c r="J3" s="3" t="n">
+        <v>1.66</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4044.48</v>
+        <v>3996.05</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$9.84</t>
+          <t>$-18.26</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4060.1</v>
+        <v>4010</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>15.62</v>
+        <v>13.95</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4132.95</v>
+        <v>4044.48</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-2.14%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$3.15</t>
+          <t>+$9.84</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4151.2</v>
+        <v>4060.1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-2.19%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>18.25</v>
+        <v>15.62</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4123.8</v>
+        <v>4132.95</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$2.14</t>
+          <t>+$3.15</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4142.6</v>
+        <v>4151.2</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>18.8</v>
+        <v>18.25</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4143.83</v>
+        <v>4123.8</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-1.16</t>
+          <t>+$2.14</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4163.1</v>
+        <v>4142.6</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>19.27</v>
+        <v>18.8</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4161.81</v>
+        <v>4143.83</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$21.36</t>
+          <t>$-1.16</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4182.2</v>
+        <v>4163.1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>20.39</v>
+        <v>19.27</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4150.36</v>
+        <v>4161.81</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$20.34</t>
+          <t>+$21.36</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4171.5</v>
+        <v>4182.2</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>21.14</v>
+        <v>20.39</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.11</v>
+        <v>0.96</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4087.97</v>
+        <v>4150.36</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.53%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$6.22</t>
+          <t>+$20.34</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4109.8</v>
+        <v>4171.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>21.83</v>
+        <v>21.14</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4154.9</v>
+        <v>4087.97</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$6.19</t>
+          <t>+$6.22</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4178.3</v>
+        <v>4109.8</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>23.4</v>
+        <v>21.83</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4167.55</v>
+        <v>4154.9</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$2.52</t>
+          <t>+$6.19</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4191.2</v>
+        <v>4178.3</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>23.65</v>
+        <v>23.4</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>4167.55</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>+$2.52</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
         <v>4191.2</v>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>+1.48%</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>$-6.33</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>4216.3</v>
-      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>25.1</v>
+        <v>23.65</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4130.14</v>
+        <v>4191.2</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-0.10</t>
+          <t>$-6.33</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4154.6</v>
+        <v>4216.3</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+1.49%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>24.46</v>
+        <v>25.1</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4114.77</v>
+        <v>4130.14</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$4.74</t>
+          <t>$-0.10</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4140.7</v>
+        <v>4154.6</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>25.93</v>
+        <v>24.46</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4162.96</v>
+        <v>4114.77</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$13.14</t>
+          <t>+$4.74</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4190.3</v>
+        <v>4140.7</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>27.34</v>
+        <v>25.93</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4129.15</v>
+        <v>4162.96</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$1.31</t>
+          <t>+$13.14</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4156.7</v>
+        <v>4190.3</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>27.55</v>
+        <v>27.34</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4139.21</v>
+        <v>4129.15</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>+$1.31</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4167.9</v>
+        <v>4156.7</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>28.69</v>
+        <v>27.55</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1784,8 +1784,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="3" t="n">
-        <v>1.38</v>
+      <c r="J27" s="4" t="n">
+        <v>1.27</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,28 +1992,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,32 +2041,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2225,8 +2225,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J36" s="3" t="n">
-        <v>1.42</v>
+      <c r="J36" s="4" t="n">
+        <v>1.35</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2274,8 +2274,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J37" s="4" t="n">
-        <v>1.32</v>
+      <c r="J37" s="3" t="n">
+        <v>1.42</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2372,44 +2372,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J39" s="3" t="n">
-        <v>1.37</v>
+      <c r="J39" s="4" t="n">
+        <v>1.34</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J40" s="3" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2433,32 +2433,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="J41" s="3" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="J42" s="3" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2568,8 +2568,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J43" s="4" t="n">
-        <v>1.26</v>
+      <c r="J43" s="3" t="n">
+        <v>1.47</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2618,43 +2618,43 @@
         </is>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2678,32 +2678,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2715,8 +2715,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J46" s="3" t="n">
-        <v>1.37</v>
+      <c r="J46" s="4" t="n">
+        <v>1.19</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2727,32 +2727,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="J47" s="3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2825,32 +2825,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="J49" s="3" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2874,32 +2874,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="J50" s="3" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2923,32 +2923,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="J51" s="3" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2972,32 +2972,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3021,32 +3021,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4417.6</v>
+        <v>4440.3</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>56.64</v>
+        <v>57.87</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="J53" s="3" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3070,32 +3070,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4410.25</v>
+        <v>4360.96</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>$-4.54</t>
+          <t>+$0.16</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4470.6</v>
+        <v>4417.6</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>60.35</v>
+        <v>56.64</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3107,8 +3107,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J54" s="4" t="n">
-        <v>1.25</v>
+      <c r="J54" s="3" t="n">
+        <v>1.49</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3119,32 +3119,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4376.76</v>
+        <v>4410.25</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+$27.56</t>
+          <t>$-4.54</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4436.1</v>
+        <v>4470.6</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>59.34</v>
+        <v>60.35</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3156,8 +3156,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J55" s="3" t="n">
-        <v>1.53</v>
+      <c r="J55" s="4" t="n">
+        <v>1.25</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3168,32 +3168,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4362.03</v>
+        <v>4376.76</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+$7.95</t>
+          <t>+$27.56</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4421.7</v>
+        <v>4436.1</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>59.67</v>
+        <v>59.34</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="J56" s="3" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3217,32 +3217,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4336.77</v>
+        <v>4362.03</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>$-2.50</t>
+          <t>+$7.95</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4396</v>
+        <v>4421.7</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>59.23</v>
+        <v>59.67</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="J57" s="3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -3266,32 +3266,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4240.53</v>
+        <v>4336.77</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>$-2.50</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4298.8</v>
+        <v>4396</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>58.27</v>
+        <v>59.23</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="J58" s="3" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3315,32 +3315,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4248.17</v>
+        <v>4240.53</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>$-15.67</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4308.3</v>
+        <v>4298.8</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>60.13</v>
+        <v>58.27</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="J59" s="3" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -3364,32 +3364,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4093.57</v>
+        <v>4248.17</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+$15.10</t>
+          <t>$-15.67</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4150.6</v>
+        <v>4308.3</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>57.03</v>
+        <v>60.13</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="J60" s="3" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -3413,32 +3413,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4034.98</v>
+        <v>4093.57</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>+$30.89</t>
+          <t>+$15.10</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4090.7</v>
+        <v>4150.6</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>55.72</v>
+        <v>57.03</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="J61" s="3" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -3462,32 +3462,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4047.78</v>
+        <v>4034.98</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>+$5.61</t>
+          <t>+$30.89</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4104.3</v>
+        <v>4090.7</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>56.52</v>
+        <v>55.72</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3499,7 +3499,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr"/>
+      <c r="J62" s="3" t="n">
+        <v>1.63</v>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -3509,32 +3511,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4100.74</v>
+        <v>4047.78</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>+$27.81</t>
+          <t>+$5.61</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4159.8</v>
+        <v>4104.3</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>59.06</v>
+        <v>56.52</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3556,32 +3558,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4038.59</v>
+        <v>4100.74</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>$-4.89</t>
+          <t>+$27.81</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4096.6</v>
+        <v>4159.8</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>58.01</v>
+        <v>59.06</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3603,32 +3605,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4035.01</v>
+        <v>4038.59</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>+$5.63</t>
+          <t>$-4.89</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4095.6</v>
+        <v>4096.6</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>60.59</v>
+        <v>58.01</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3650,32 +3652,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4073.78</v>
+        <v>4035.01</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>+$28.32</t>
+          <t>+$5.63</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4134.8</v>
+        <v>4095.6</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>61.02</v>
+        <v>60.59</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3697,32 +3699,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4068.52</v>
+        <v>4073.78</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>+$2.67</t>
+          <t>+$28.32</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4130.3</v>
+        <v>4134.8</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>61.78</v>
+        <v>61.02</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3744,32 +3746,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4047.38</v>
+        <v>4068.52</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>$-25.07</t>
+          <t>+$2.67</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4108.8</v>
+        <v>4130.3</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>61.42</v>
+        <v>61.78</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3791,32 +3793,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4144.43</v>
+        <v>4047.38</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>+$9.28</t>
+          <t>$-25.07</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4210.7</v>
+        <v>4108.8</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>66.27</v>
+        <v>61.42</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3838,32 +3840,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4070.53</v>
+        <v>4144.43</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>$-2.12</t>
+          <t>+$9.28</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4132.1</v>
+        <v>4210.7</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>61.57</v>
+        <v>66.27</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3885,32 +3887,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4012.2</v>
+        <v>4070.53</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>$-7.62</t>
+          <t>$-2.12</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4073.4</v>
+        <v>4132.1</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3932,32 +3934,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4012.43</v>
+        <v>4012.2</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>$-6.74</t>
+          <t>$-7.62</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4073.6</v>
+        <v>4073.4</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>61.17</v>
+        <v>61.2</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3979,32 +3981,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3984.41</v>
+        <v>4012.43</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>+$10.46</t>
+          <t>$-6.74</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4045.5</v>
+        <v>4073.6</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -4026,32 +4028,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4054.39</v>
+        <v>3984.41</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>$-8.81</t>
+          <t>+$10.46</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4119.5</v>
+        <v>4045.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>65.11</v>
+        <v>61.09</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -4073,32 +4075,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4062.2</v>
+        <v>4054.39</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$-8.81</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4127.5</v>
+        <v>4119.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>65.3</v>
+        <v>65.11</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -4112,6 +4114,53 @@
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>4127.5</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -522,32 +522,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4056.06</v>
+        <v>4039</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$2.81</t>
+          <t>+$4.93</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4078.3</v>
+        <v>4054</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>22.24</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.58</v>
+        <v>1.99</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4015.69</v>
+        <v>4056.06</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$2.20</t>
+          <t>+$2.81</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4038.2</v>
+        <v>4078.3</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>22.51</v>
+        <v>22.24</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3996.05</v>
+        <v>4015.69</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-18.26</t>
+          <t>+$2.20</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4010</v>
+        <v>4038.2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>13.95</v>
+        <v>22.51</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -657,8 +657,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>1.06</v>
+      <c r="J4" s="3" t="n">
+        <v>1.66</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -669,32 +669,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4044.48</v>
+        <v>3996.05</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$9.84</t>
+          <t>$-18.26</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4060.1</v>
+        <v>4010</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>15.62</v>
+        <v>13.95</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -718,32 +718,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4132.95</v>
+        <v>4044.48</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-2.14%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$3.15</t>
+          <t>+$9.84</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4151.2</v>
+        <v>4060.1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-2.19%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>18.25</v>
+        <v>15.62</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -767,32 +767,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4123.8</v>
+        <v>4132.95</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$2.14</t>
+          <t>+$3.15</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4142.6</v>
+        <v>4151.2</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>18.8</v>
+        <v>18.25</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -816,32 +816,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4143.83</v>
+        <v>4123.8</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-1.16</t>
+          <t>+$2.14</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4163.1</v>
+        <v>4142.6</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>19.27</v>
+        <v>18.8</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4161.81</v>
+        <v>4143.83</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$21.36</t>
+          <t>$-1.16</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4182.2</v>
+        <v>4163.1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>20.39</v>
+        <v>19.27</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -914,32 +914,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4150.36</v>
+        <v>4161.81</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$20.34</t>
+          <t>+$21.36</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4171.5</v>
+        <v>4182.2</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>21.14</v>
+        <v>20.39</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.11</v>
+        <v>0.96</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -963,32 +963,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4087.97</v>
+        <v>4150.36</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.53%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$6.22</t>
+          <t>+$20.34</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4109.8</v>
+        <v>4171.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>21.83</v>
+        <v>21.14</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1012,32 +1012,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4154.9</v>
+        <v>4087.97</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$6.19</t>
+          <t>+$6.22</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4178.3</v>
+        <v>4109.8</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>23.4</v>
+        <v>21.83</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1061,32 +1061,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4167.55</v>
+        <v>4154.9</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$2.52</t>
+          <t>+$6.19</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4191.2</v>
+        <v>4178.3</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>23.65</v>
+        <v>23.4</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>4167.55</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>+$2.52</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
         <v>4191.2</v>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>+1.48%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>$-6.33</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>4216.3</v>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>25.1</v>
+        <v>23.65</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1159,32 +1159,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4130.14</v>
+        <v>4191.2</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-0.10</t>
+          <t>$-6.33</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4154.6</v>
+        <v>4216.3</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+1.49%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>24.46</v>
+        <v>25.1</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1208,32 +1208,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4114.77</v>
+        <v>4130.14</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$4.74</t>
+          <t>$-0.10</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4140.7</v>
+        <v>4154.6</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>25.93</v>
+        <v>24.46</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4162.96</v>
+        <v>4114.77</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$13.14</t>
+          <t>+$4.74</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4190.3</v>
+        <v>4140.7</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>27.34</v>
+        <v>25.93</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1306,32 +1306,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4129.15</v>
+        <v>4162.96</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$1.31</t>
+          <t>+$13.14</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4156.7</v>
+        <v>4190.3</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>27.55</v>
+        <v>27.34</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4139.21</v>
+        <v>4129.15</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>+$1.31</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4167.9</v>
+        <v>4156.7</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>28.69</v>
+        <v>27.55</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1404,32 +1404,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4175.21</v>
+        <v>4139.21</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$10.43</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4206.1</v>
+        <v>4167.9</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>30.89</v>
+        <v>28.69</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1453,32 +1453,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4150.79</v>
+        <v>4175.21</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$36.18</t>
+          <t>+$10.43</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4181.6</v>
+        <v>4206.1</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>30.81</v>
+        <v>30.89</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1502,32 +1502,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4147.7</v>
+        <v>4150.79</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-18.87</t>
+          <t>+$36.18</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4179.8</v>
+        <v>4181.6</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>32.1</v>
+        <v>30.81</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1551,32 +1551,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4136.86</v>
+        <v>4147.7</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-7.09</t>
+          <t>$-18.87</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4169.2</v>
+        <v>4179.8</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>32.34</v>
+        <v>32.1</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1600,32 +1600,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4284.86</v>
+        <v>4136.86</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$5.12</t>
+          <t>$-7.09</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4320.1</v>
+        <v>4169.2</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>35.24</v>
+        <v>32.34</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1649,32 +1649,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4263.08</v>
+        <v>4284.86</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$7.46</t>
+          <t>+$5.12</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4298.3</v>
+        <v>4320.1</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>35.22</v>
+        <v>35.24</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4280.86</v>
+        <v>4263.08</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$22.68</t>
+          <t>+$7.46</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4317</v>
+        <v>4298.3</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>36.14</v>
+        <v>35.22</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4336.36</v>
+        <v>4280.86</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$4.70</t>
+          <t>+$22.68</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4374.3</v>
+        <v>4317</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>37.94</v>
+        <v>36.14</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1796,32 +1796,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4338.92</v>
+        <v>4336.36</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-15.93</t>
+          <t>+$4.70</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4376.9</v>
+        <v>4374.3</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1833,8 +1833,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="3" t="n">
-        <v>1.38</v>
+      <c r="J28" s="4" t="n">
+        <v>1.27</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1845,32 +1845,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4392.71</v>
+        <v>4338.92</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-19.25</t>
+          <t>$-15.93</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4431.4</v>
+        <v>4376.9</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>38.69</v>
+        <v>37.98</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1894,32 +1894,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4362.36</v>
+        <v>4392.71</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-85.16</t>
+          <t>$-19.25</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4402</v>
+        <v>4431.4</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>39.64</v>
+        <v>38.69</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1943,32 +1943,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4348.5</v>
+        <v>4362.36</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$0.47</t>
+          <t>$-85.16</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4390.5</v>
+        <v>4402</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>42</v>
+        <v>39.64</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1992,32 +1992,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4297.04</v>
+        <v>4348.5</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-8.60</t>
+          <t>+$0.47</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4337.8</v>
+        <v>4390.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>40.76</v>
+        <v>42</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2041,28 +2041,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4308.94</v>
+        <v>4297.04</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-44.22</t>
+          <t>$-8.60</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4349.7</v>
+        <v>4337.8</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2090,32 +2090,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4368.9</v>
+        <v>4308.94</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$-42.03</t>
+          <t>$-44.22</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4411.5</v>
+        <v>4349.7</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>42.6</v>
+        <v>40.76</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4362.82</v>
+        <v>4368.9</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-7.86</t>
+          <t>$-42.03</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4404.4</v>
+        <v>4411.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>41.58</v>
+        <v>42.6</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4412.58</v>
+        <v>4362.82</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-31.36</t>
+          <t>$-7.86</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4457.7</v>
+        <v>4404.4</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>45.12</v>
+        <v>41.58</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2225,8 +2225,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J36" s="4" t="n">
-        <v>1.35</v>
+      <c r="J36" s="3" t="n">
+        <v>1.54</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4391.69</v>
+        <v>4412.58</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>$-10.99</t>
+          <t>$-31.36</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4436.1</v>
+        <v>4457.7</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>44.41</v>
+        <v>45.12</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2274,8 +2274,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J37" s="3" t="n">
-        <v>1.42</v>
+      <c r="J37" s="4" t="n">
+        <v>1.35</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2286,32 +2286,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4424</v>
+        <v>4391.69</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>$-18.76</t>
+          <t>$-10.99</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4471.5</v>
+        <v>4436.1</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>47.5</v>
+        <v>44.41</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2323,8 +2323,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J38" s="4" t="n">
-        <v>1.32</v>
+      <c r="J38" s="3" t="n">
+        <v>1.42</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4491.75</v>
+        <v>4424</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$18.29</t>
+          <t>$-18.76</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4539.2</v>
+        <v>4471.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4368.02</v>
+        <v>4491.75</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-14.42</t>
+          <t>+$18.29</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4414.7</v>
+        <v>4539.2</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>46.68</v>
+        <v>47.45</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2421,44 +2421,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J40" s="3" t="n">
-        <v>1.37</v>
+      <c r="J40" s="4" t="n">
+        <v>1.34</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4347.7</v>
+        <v>4368.02</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$16.33</t>
+          <t>$-14.42</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4395.8</v>
+        <v>4414.7</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="J41" s="3" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2482,32 +2482,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4432.42</v>
+        <v>4347.7</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>$-46.10</t>
+          <t>+$16.33</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4482.1</v>
+        <v>4395.8</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>49.68</v>
+        <v>48.1</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="J42" s="3" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4478.51</v>
+        <v>4432.42</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>$-7.02</t>
+          <t>$-46.10</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4528.9</v>
+        <v>4482.1</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>50.39</v>
+        <v>49.68</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="J43" s="3" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4610.08</v>
+        <v>4478.51</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>$-4.59</t>
+          <t>$-7.02</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4663.9</v>
+        <v>4528.9</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>53.82</v>
+        <v>50.39</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2617,8 +2617,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J44" s="4" t="n">
-        <v>1.26</v>
+      <c r="J44" s="3" t="n">
+        <v>1.47</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4600.96</v>
+        <v>4610.08</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$19.62</t>
+          <t>$-4.59</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4656.3</v>
+        <v>4663.9</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>55.34</v>
+        <v>53.82</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2667,43 +2667,43 @@
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4638.15</v>
+        <v>4600.96</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$15.84</t>
+          <t>+$19.62</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4695.7</v>
+        <v>4656.3</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>57.55</v>
+        <v>55.34</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="J46" s="4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2727,32 +2727,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4637.46</v>
+        <v>4638.15</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>$-6.19</t>
+          <t>+$15.84</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4694.5</v>
+        <v>4695.7</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>57.04</v>
+        <v>57.55</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2764,8 +2764,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J47" s="3" t="n">
-        <v>1.37</v>
+      <c r="J47" s="4" t="n">
+        <v>1.19</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4620.76</v>
+        <v>4637.46</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+$0.29</t>
+          <t>$-6.19</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4678.6</v>
+        <v>4694.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>57.84</v>
+        <v>57.04</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2825,32 +2825,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4518.38</v>
+        <v>4620.76</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+$29.94</t>
+          <t>+$0.29</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4575</v>
+        <v>4678.6</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>56.62</v>
+        <v>57.84</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="J49" s="3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2874,32 +2874,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4488.38</v>
+        <v>4518.38</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$-30.46</t>
+          <t>+$29.94</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4545.9</v>
+        <v>4575</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+2.85%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>57.52</v>
+        <v>56.62</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="J50" s="3" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2923,32 +2923,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4364.25</v>
+        <v>4488.38</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+$0.63</t>
+          <t>$-30.46</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4420.1</v>
+        <v>4545.9</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.85%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>55.85</v>
+        <v>57.52</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="J51" s="3" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2972,32 +2972,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4417.13</v>
+        <v>4364.25</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>$-3.16</t>
+          <t>+$0.63</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4474.7</v>
+        <v>4420.1</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>57.57</v>
+        <v>55.85</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="J52" s="3" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3021,32 +3021,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4382.43</v>
+        <v>4417.13</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>$-7.19</t>
+          <t>$-3.16</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4440.3</v>
+        <v>4474.7</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3070,32 +3070,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4360.96</v>
+        <v>4382.43</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+$0.16</t>
+          <t>$-7.19</t>
         </is>
       </c>
       <c r="E54" t=